--- a/Reportes_Auditoria_2026-02-28/AUDITORIA_OFICIAL_SISTEMA_2026-02-28_PULIDO.xlsx
+++ b/Reportes_Auditoria_2026-02-28/AUDITORIA_OFICIAL_SISTEMA_2026-02-28_PULIDO.xlsx
@@ -33,38 +33,38 @@
       <name val="Segoe UI"/>
       <b val="1"/>
       <color rgb="000F172A"/>
-      <sz val="14"/>
+      <sz val="13"/>
     </font>
     <font>
       <name val="Segoe UI"/>
       <b val="1"/>
       <color rgb="00475569"/>
-      <sz val="10"/>
+      <sz val="9.5"/>
     </font>
     <font>
       <name val="Segoe UI"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="10"/>
+      <sz val="9.5"/>
     </font>
     <font>
       <name val="Segoe UI"/>
-      <sz val="9.5"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Consolas"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Segoe UI"/>
       <b val="1"/>
+      <color rgb="000F172A"/>
       <sz val="9.5"/>
-    </font>
-    <font>
-      <name val="Segoe UI"/>
-      <b val="1"/>
-      <color rgb="000F172A"/>
-      <sz val="10"/>
     </font>
   </fonts>
   <fills count="5">
@@ -560,10 +560,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O40"/>
+  <dimension ref="A1:O39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
     <col width="38" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
@@ -580,7 +580,7 @@
     <col width="16" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
+    <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>INANDES GRUPO FINANCIERO &amp; GEEKSOFT — AUDITORÍA Y CIERRE CONTABLE</t>
@@ -590,7 +590,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Período: 01/01/2026 al 28/02/2026 (59 Días Base 365)  |  Fondo: NSGPEN01 (PEN)  |  Total Inversionistas: 35</t>
+          <t>Período: 01/01/2026 al 28/02/2026 (59 Días Base 365)  |  Fondo: NSGPEN01 (PEN)  |  Total Inversionistas: 34</t>
         </is>
       </c>
     </row>
@@ -709,19 +709,19 @@
       <c r="J5" s="11" t="n">
         <v>30635.55</v>
       </c>
-      <c r="K5" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" s="11" t="n">
+      <c r="K5" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="10" t="n">
         <v>30635.55</v>
       </c>
       <c r="M5" s="11" t="n">
         <v>325000</v>
       </c>
-      <c r="N5" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" s="11" t="n">
+      <c r="N5" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="10" t="n">
         <v>1575000</v>
       </c>
     </row>
@@ -762,19 +762,19 @@
       <c r="J6" s="17" t="n">
         <v>9674.379999999999</v>
       </c>
-      <c r="K6" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="17" t="n">
+      <c r="K6" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="16" t="n">
         <v>9674.379999999999</v>
       </c>
       <c r="M6" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="N6" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" s="17" t="n">
+      <c r="N6" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="16" t="n">
         <v>600000</v>
       </c>
     </row>
@@ -815,19 +815,19 @@
       <c r="J7" s="11" t="n">
         <v>1289.92</v>
       </c>
-      <c r="K7" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="11" t="n">
+      <c r="K7" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="10" t="n">
         <v>1289.92</v>
       </c>
       <c r="M7" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N7" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" s="11" t="n">
+      <c r="N7" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="10" t="n">
         <v>80000</v>
       </c>
     </row>
@@ -868,19 +868,19 @@
       <c r="J8" s="17" t="n">
         <v>1612.4</v>
       </c>
-      <c r="K8" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" s="17" t="n">
+      <c r="K8" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="16" t="n">
         <v>1612.4</v>
       </c>
       <c r="M8" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="N8" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" s="17" t="n">
+      <c r="N8" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="16" t="n">
         <v>100000</v>
       </c>
     </row>
@@ -921,19 +921,19 @@
       <c r="J9" s="11" t="n">
         <v>5401.53</v>
       </c>
-      <c r="K9" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" s="11" t="n">
+      <c r="K9" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="10" t="n">
         <v>5401.53</v>
       </c>
       <c r="M9" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N9" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" s="11" t="n">
+      <c r="N9" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="10" t="n">
         <v>335000</v>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="C10" s="14" t="inlineStr">
         <is>
-          <t>Barton Carmen Michele</t>
+          <t xml:space="preserve">Barton Carmen Michele </t>
         </is>
       </c>
       <c r="D10" s="15" t="inlineStr">
@@ -974,19 +974,19 @@
       <c r="J10" s="17" t="n">
         <v>967.4400000000001</v>
       </c>
-      <c r="K10" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" s="17" t="n">
+      <c r="K10" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="16" t="n">
         <v>967.4400000000001</v>
       </c>
       <c r="M10" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="N10" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" s="17" t="n">
+      <c r="N10" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="16" t="n">
         <v>60000</v>
       </c>
     </row>
@@ -1027,19 +1027,19 @@
       <c r="J11" s="11" t="n">
         <v>1048.06</v>
       </c>
-      <c r="K11" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" s="11" t="n">
+      <c r="K11" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="10" t="n">
         <v>1048.06</v>
       </c>
       <c r="M11" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N11" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" s="11" t="n">
+      <c r="N11" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="10" t="n">
         <v>65000</v>
       </c>
     </row>
@@ -1080,19 +1080,19 @@
       <c r="J12" s="17" t="n">
         <v>2418.6</v>
       </c>
-      <c r="K12" s="16" t="n">
+      <c r="K12" s="17" t="n">
         <v>873.4400000000001</v>
       </c>
-      <c r="L12" s="17" t="n">
+      <c r="L12" s="16" t="n">
         <v>1545.16</v>
       </c>
       <c r="M12" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="N12" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" s="17" t="n">
+      <c r="N12" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="16" t="n">
         <v>150000</v>
       </c>
     </row>
@@ -1133,19 +1133,19 @@
       <c r="J13" s="11" t="n">
         <v>2257.35</v>
       </c>
-      <c r="K13" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" s="11" t="n">
+      <c r="K13" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="10" t="n">
         <v>2257.35</v>
       </c>
       <c r="M13" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N13" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" s="11" t="n">
+      <c r="N13" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="10" t="n">
         <v>140000</v>
       </c>
     </row>
@@ -1186,19 +1186,19 @@
       <c r="J14" s="17" t="n">
         <v>1612.4</v>
       </c>
-      <c r="K14" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" s="17" t="n">
+      <c r="K14" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="16" t="n">
         <v>1612.4</v>
       </c>
       <c r="M14" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="N14" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" s="17" t="n">
+      <c r="N14" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="16" t="n">
         <v>100000</v>
       </c>
     </row>
@@ -1239,19 +1239,19 @@
       <c r="J15" s="11" t="n">
         <v>9674.379999999999</v>
       </c>
-      <c r="K15" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" s="11" t="n">
+      <c r="K15" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="10" t="n">
         <v>9674.379999999999</v>
       </c>
       <c r="M15" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N15" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" s="11" t="n">
+      <c r="N15" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" s="10" t="n">
         <v>600000</v>
       </c>
     </row>
@@ -1292,19 +1292,19 @@
       <c r="J16" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="K16" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" s="17" t="n">
+      <c r="K16" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="16" t="n">
         <v>0</v>
       </c>
       <c r="M16" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="N16" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" s="17" t="n">
+      <c r="N16" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" s="16" t="n">
         <v>641505.28</v>
       </c>
     </row>
@@ -1312,8 +1312,10 @@
       <c r="A17" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="7" t="n">
-        <v/>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>NSGPEN01-046.20160101.20251231</t>
+        </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
@@ -1343,19 +1345,19 @@
       <c r="J17" s="11" t="n">
         <v>806.2</v>
       </c>
-      <c r="K17" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" s="11" t="n">
-        <v>806.2</v>
+      <c r="K17" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="M17" s="11" t="n">
         <v>50000</v>
       </c>
-      <c r="N17" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" s="11" t="n">
+      <c r="N17" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1396,19 +1398,19 @@
       <c r="J18" s="17" t="n">
         <v>4837.19</v>
       </c>
-      <c r="K18" s="16" t="n">
+      <c r="K18" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="L18" s="17" t="n">
+      <c r="L18" s="16" t="n">
         <v>4837.19</v>
       </c>
       <c r="M18" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="N18" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" s="17" t="n">
+      <c r="N18" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" s="16" t="n">
         <v>300000</v>
       </c>
     </row>
@@ -1449,19 +1451,19 @@
       <c r="J19" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="K19" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" s="11" t="n">
+      <c r="K19" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="10" t="n">
         <v>0</v>
       </c>
       <c r="M19" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N19" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" s="11" t="n">
+      <c r="N19" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" s="10" t="n">
         <v>422448.25</v>
       </c>
     </row>
@@ -1476,7 +1478,7 @@
       </c>
       <c r="C20" s="14" t="inlineStr">
         <is>
-          <t>Xiangyan  Tao</t>
+          <t xml:space="preserve">Xiangyan  Tao </t>
         </is>
       </c>
       <c r="D20" s="15" t="inlineStr">
@@ -1502,19 +1504,19 @@
       <c r="J20" s="17" t="n">
         <v>1733.48</v>
       </c>
-      <c r="K20" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" s="17" t="n">
+      <c r="K20" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="16" t="n">
         <v>1733.48</v>
       </c>
       <c r="M20" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="N20" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" s="17" t="n">
+      <c r="N20" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" s="16" t="n">
         <v>107509.52</v>
       </c>
     </row>
@@ -1555,19 +1557,19 @@
       <c r="J21" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="K21" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" s="11" t="n">
+      <c r="K21" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="10" t="n">
         <v>0</v>
       </c>
       <c r="M21" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N21" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" s="11" t="n">
+      <c r="N21" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" s="10" t="n">
         <v>513863.62</v>
       </c>
     </row>
@@ -1608,19 +1610,19 @@
       <c r="J22" s="17" t="n">
         <v>838.45</v>
       </c>
-      <c r="K22" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" s="17" t="n">
+      <c r="K22" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="16" t="n">
         <v>838.45</v>
       </c>
       <c r="M22" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="N22" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" s="17" t="n">
+      <c r="N22" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" s="16" t="n">
         <v>52000</v>
       </c>
     </row>
@@ -1661,19 +1663,19 @@
       <c r="J23" s="11" t="n">
         <v>6449.59</v>
       </c>
-      <c r="K23" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" s="11" t="n">
+      <c r="K23" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" s="10" t="n">
         <v>6449.59</v>
       </c>
       <c r="M23" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N23" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" s="11" t="n">
+      <c r="N23" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" s="10" t="n">
         <v>400000</v>
       </c>
     </row>
@@ -1714,19 +1716,19 @@
       <c r="J24" s="17" t="n">
         <v>982.39</v>
       </c>
-      <c r="K24" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" s="17" t="n">
+      <c r="K24" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="16" t="n">
         <v>982.39</v>
       </c>
       <c r="M24" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="N24" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" s="17" t="n">
+      <c r="N24" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" s="16" t="n">
         <v>60926.96</v>
       </c>
     </row>
@@ -1767,19 +1769,19 @@
       <c r="J25" s="11" t="n">
         <v>2257.35</v>
       </c>
-      <c r="K25" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" s="11" t="n">
+      <c r="K25" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="10" t="n">
         <v>2257.35</v>
       </c>
       <c r="M25" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N25" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" s="11" t="n">
+      <c r="N25" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" s="10" t="n">
         <v>140000</v>
       </c>
     </row>
@@ -1820,19 +1822,19 @@
       <c r="J26" s="17" t="n">
         <v>10760.28</v>
       </c>
-      <c r="K26" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" s="17" t="n">
+      <c r="K26" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="16" t="n">
         <v>10760.28</v>
       </c>
       <c r="M26" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="N26" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" s="17" t="n">
+      <c r="N26" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" s="16" t="n">
         <v>667346.45</v>
       </c>
     </row>
@@ -1847,7 +1849,7 @@
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>Sánchez Santillán Teresa de Jesús</t>
+          <t xml:space="preserve">Sánchez Santillán Teresa de Jesús </t>
         </is>
       </c>
       <c r="D27" s="9" t="inlineStr">
@@ -1873,19 +1875,19 @@
       <c r="J27" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="K27" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" s="11" t="n">
+      <c r="K27" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="10" t="n">
         <v>0</v>
       </c>
       <c r="M27" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N27" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" s="11" t="n">
+      <c r="N27" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" s="10" t="n">
         <v>183946.29</v>
       </c>
     </row>
@@ -1926,19 +1928,19 @@
       <c r="J28" s="17" t="n">
         <v>2773.33</v>
       </c>
-      <c r="K28" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" s="17" t="n">
+      <c r="K28" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="16" t="n">
         <v>2773.33</v>
       </c>
       <c r="M28" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="N28" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" s="17" t="n">
+      <c r="N28" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" s="16" t="n">
         <v>172000</v>
       </c>
     </row>
@@ -1979,19 +1981,19 @@
       <c r="J29" s="11" t="n">
         <v>1773.64</v>
       </c>
-      <c r="K29" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" s="11" t="n">
+      <c r="K29" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="10" t="n">
         <v>1773.64</v>
       </c>
       <c r="M29" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N29" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" s="11" t="n">
+      <c r="N29" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" s="10" t="n">
         <v>110000</v>
       </c>
     </row>
@@ -2032,19 +2034,19 @@
       <c r="J30" s="17" t="n">
         <v>3708.51</v>
       </c>
-      <c r="K30" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" s="17" t="n">
+      <c r="K30" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" s="16" t="n">
         <v>3708.51</v>
       </c>
       <c r="M30" s="17" t="n">
         <v>10000</v>
       </c>
-      <c r="N30" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" s="17" t="n">
+      <c r="N30" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" s="16" t="n">
         <v>220000</v>
       </c>
     </row>
@@ -2059,7 +2061,7 @@
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>Araujo Novoa Carlos Alfonso / Rojas Ibañez de Araujo Jacqueline</t>
+          <t xml:space="preserve">Araujo Novoa Carlos Alfonso / Rojas Ibañez de Araujo Jacqueline </t>
         </is>
       </c>
       <c r="D31" s="9" t="inlineStr">
@@ -2085,19 +2087,19 @@
       <c r="J31" s="11" t="n">
         <v>806.2</v>
       </c>
-      <c r="K31" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" s="11" t="n">
+      <c r="K31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" s="10" t="n">
         <v>806.2</v>
       </c>
       <c r="M31" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N31" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" s="11" t="n">
+      <c r="N31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" s="10" t="n">
         <v>50000</v>
       </c>
     </row>
@@ -2138,19 +2140,19 @@
       <c r="J32" s="17" t="n">
         <v>3224.79</v>
       </c>
-      <c r="K32" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" s="17" t="n">
+      <c r="K32" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="16" t="n">
         <v>3224.79</v>
       </c>
       <c r="M32" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="N32" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" s="17" t="n">
+      <c r="N32" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" s="16" t="n">
         <v>200000</v>
       </c>
     </row>
@@ -2191,19 +2193,19 @@
       <c r="J33" s="11" t="n">
         <v>1612.4</v>
       </c>
-      <c r="K33" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" s="11" t="n">
+      <c r="K33" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="10" t="n">
         <v>1612.4</v>
       </c>
       <c r="M33" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N33" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" s="11" t="n">
+      <c r="N33" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" s="10" t="n">
         <v>100000</v>
       </c>
     </row>
@@ -2244,19 +2246,19 @@
       <c r="J34" s="17" t="n">
         <v>16607.69</v>
       </c>
-      <c r="K34" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" s="17" t="n">
+      <c r="K34" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="16" t="n">
         <v>16607.69</v>
       </c>
       <c r="M34" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="N34" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" s="17" t="n">
+      <c r="N34" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" s="16" t="n">
         <v>1030000</v>
       </c>
     </row>
@@ -2297,19 +2299,19 @@
       <c r="J35" s="11" t="n">
         <v>5965.87</v>
       </c>
-      <c r="K35" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" s="11" t="n">
+      <c r="K35" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="10" t="n">
         <v>5965.87</v>
       </c>
       <c r="M35" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N35" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" s="11" t="n">
+      <c r="N35" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" s="10" t="n">
         <v>370000</v>
       </c>
     </row>
@@ -2350,19 +2352,19 @@
       <c r="J36" s="17" t="n">
         <v>3547.27</v>
       </c>
-      <c r="K36" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" s="17" t="n">
+      <c r="K36" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="16" t="n">
         <v>3547.27</v>
       </c>
       <c r="M36" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="N36" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" s="17" t="n">
+      <c r="N36" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" s="16" t="n">
         <v>220000</v>
       </c>
     </row>
@@ -2403,19 +2405,19 @@
       <c r="J37" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="K37" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" s="11" t="n">
+      <c r="K37" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" s="10" t="n">
         <v>0</v>
       </c>
       <c r="M37" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N37" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O37" s="11" t="n">
+      <c r="N37" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" s="10" t="n">
         <v>40870.44</v>
       </c>
     </row>
@@ -2456,135 +2458,84 @@
       <c r="J38" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="K38" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" s="17" t="n">
+      <c r="K38" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" s="16" t="n">
         <v>0</v>
       </c>
       <c r="M38" s="17" t="n">
         <v>81213.35000000001</v>
       </c>
-      <c r="N38" s="16" t="n">
+      <c r="N38" s="17" t="n">
         <v>169000</v>
       </c>
-      <c r="O38" s="17" t="n">
+      <c r="O38" s="16" t="n">
         <v>314692.85</v>
       </c>
     </row>
-    <row r="39" ht="19" customHeight="1">
-      <c r="A39" s="6" t="n">
+    <row r="39" ht="22" customHeight="1">
+      <c r="A39" s="18" t="inlineStr"/>
+      <c r="B39" s="19" t="inlineStr"/>
+      <c r="C39" s="19" t="inlineStr">
+        <is>
+          <t>TOTALES NSGPEN01 (PEN)</t>
+        </is>
+      </c>
+      <c r="D39" s="18" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="E39" s="20">
+        <f>SUM(E5:E38)</f>
         <v/>
       </c>
-      <c r="B39" s="7" t="n">
+      <c r="F39" s="20">
+        <f>SUM(F5:F38)</f>
         <v/>
       </c>
-      <c r="C39" s="8" t="inlineStr">
-        <is>
-          <t>TOTALES NSGPEN01 (PEN)</t>
-        </is>
-      </c>
-      <c r="D39" s="9" t="inlineStr">
-        <is>
-          <t>PEN</t>
-        </is>
-      </c>
-      <c r="E39" s="10" t="n">
+      <c r="G39" s="20">
+        <f>SUM(G5:G38)</f>
         <v/>
       </c>
-      <c r="F39" s="10" t="n">
+      <c r="H39" s="20">
+        <f>SUM(H5:H38)</f>
         <v/>
       </c>
-      <c r="G39" s="11" t="n">
+      <c r="I39" s="20">
+        <f>SUM(I5:I38)</f>
         <v/>
       </c>
-      <c r="H39" s="11" t="n">
+      <c r="J39" s="20">
+        <f>SUM(J5:J38)</f>
         <v/>
       </c>
-      <c r="I39" s="11" t="n">
+      <c r="K39" s="20">
+        <f>SUM(K5:K38)</f>
         <v/>
       </c>
-      <c r="J39" s="11" t="n">
+      <c r="L39" s="20">
+        <f>SUM(L5:L38)</f>
         <v/>
       </c>
-      <c r="K39" s="10" t="n">
+      <c r="M39" s="20">
+        <f>SUM(M5:M38)</f>
         <v/>
       </c>
-      <c r="L39" s="11" t="n">
+      <c r="N39" s="20">
+        <f>SUM(N5:N38)</f>
         <v/>
       </c>
-      <c r="M39" s="11" t="n">
-        <v/>
-      </c>
-      <c r="N39" s="10" t="n">
-        <v/>
-      </c>
-      <c r="O39" s="11" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="40" ht="22" customHeight="1">
-      <c r="A40" s="18" t="inlineStr"/>
-      <c r="B40" s="19" t="inlineStr"/>
-      <c r="C40" s="19" t="inlineStr">
-        <is>
-          <t>TOTALES NSGPEN01 (PEN)</t>
-        </is>
-      </c>
-      <c r="D40" s="18" t="inlineStr">
-        <is>
-          <t>PEN</t>
-        </is>
-      </c>
-      <c r="E40" s="20">
-        <f>SUM(E5:E39)</f>
-        <v/>
-      </c>
-      <c r="F40" s="20">
-        <f>SUM(F5:F39)</f>
-        <v/>
-      </c>
-      <c r="G40" s="20">
-        <f>SUM(G5:G39)</f>
-        <v/>
-      </c>
-      <c r="H40" s="20">
-        <f>SUM(H5:H39)</f>
-        <v/>
-      </c>
-      <c r="I40" s="20">
-        <f>SUM(I5:I39)</f>
-        <v/>
-      </c>
-      <c r="J40" s="20">
-        <f>SUM(J5:J39)</f>
-        <v/>
-      </c>
-      <c r="K40" s="20">
-        <f>SUM(K5:K39)</f>
-        <v/>
-      </c>
-      <c r="L40" s="20">
-        <f>SUM(L5:L39)</f>
-        <v/>
-      </c>
-      <c r="M40" s="20">
-        <f>SUM(M5:M39)</f>
-        <v/>
-      </c>
-      <c r="N40" s="20">
-        <f>SUM(N5:N39)</f>
-        <v/>
-      </c>
-      <c r="O40" s="20">
-        <f>SUM(O5:O39)</f>
+      <c r="O39" s="20">
+        <f>SUM(O5:O38)</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:N2"/>
-    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A2:O2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2596,10 +2547,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O31"/>
+  <dimension ref="A1:O30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
     <col width="38" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
@@ -2616,7 +2567,7 @@
     <col width="16" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
+    <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>INANDES GRUPO FINANCIERO &amp; GEEKSOFT — AUDITORÍA Y CIERRE CONTABLE</t>
@@ -2626,7 +2577,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Período: 01/01/2026 al 28/02/2026 (59 Días Base 365)  |  Fondo: NSGPEN02 (PEN)  |  Total Inversionistas: 26</t>
+          <t>Período: 01/01/2026 al 28/02/2026 (59 Días Base 365)  |  Fondo: NSGPEN02 (PEN)  |  Total Inversionistas: 25</t>
         </is>
       </c>
     </row>
@@ -2745,19 +2696,19 @@
       <c r="J5" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="K5" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" s="11" t="n">
+      <c r="K5" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="10" t="n">
         <v>0</v>
       </c>
       <c r="M5" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N5" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" s="11" t="n">
+      <c r="N5" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="10" t="n">
         <v>171413.89</v>
       </c>
     </row>
@@ -2798,19 +2749,19 @@
       <c r="J6" s="17" t="n">
         <v>2840.89</v>
       </c>
-      <c r="K6" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="17" t="n">
+      <c r="K6" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="16" t="n">
         <v>2840.89</v>
       </c>
       <c r="M6" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="N6" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" s="17" t="n">
+      <c r="N6" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="16" t="n">
         <v>185000</v>
       </c>
     </row>
@@ -2851,19 +2802,19 @@
       <c r="J7" s="11" t="n">
         <v>13820.55</v>
       </c>
-      <c r="K7" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="11" t="n">
+      <c r="K7" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="10" t="n">
         <v>13820.55</v>
       </c>
       <c r="M7" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N7" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" s="11" t="n">
+      <c r="N7" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="10" t="n">
         <v>900000</v>
       </c>
     </row>
@@ -2904,19 +2855,19 @@
       <c r="J8" s="17" t="n">
         <v>1458.84</v>
       </c>
-      <c r="K8" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" s="17" t="n">
+      <c r="K8" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="16" t="n">
         <v>1458.84</v>
       </c>
       <c r="M8" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="N8" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" s="17" t="n">
+      <c r="N8" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="16" t="n">
         <v>100000</v>
       </c>
     </row>
@@ -2957,19 +2908,19 @@
       <c r="J9" s="11" t="n">
         <v>1535.62</v>
       </c>
-      <c r="K9" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" s="11" t="n">
+      <c r="K9" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="10" t="n">
         <v>1535.62</v>
       </c>
       <c r="M9" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N9" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" s="11" t="n">
+      <c r="N9" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="10" t="n">
         <v>100000</v>
       </c>
     </row>
@@ -3010,19 +2961,19 @@
       <c r="J10" s="17" t="n">
         <v>2290.46</v>
       </c>
-      <c r="K10" s="16" t="n">
+      <c r="K10" s="17" t="n">
         <v>200.91</v>
       </c>
-      <c r="L10" s="17" t="n">
+      <c r="L10" s="16" t="n">
         <v>2089.55</v>
       </c>
       <c r="M10" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="N10" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" s="17" t="n">
+      <c r="N10" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="16" t="n">
         <v>157005.93</v>
       </c>
     </row>
@@ -3063,19 +3014,19 @@
       <c r="J11" s="11" t="n">
         <v>1458.84</v>
       </c>
-      <c r="K11" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" s="11" t="n">
+      <c r="K11" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="10" t="n">
         <v>1458.84</v>
       </c>
       <c r="M11" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N11" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" s="11" t="n">
+      <c r="N11" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="10" t="n">
         <v>100000</v>
       </c>
     </row>
@@ -3116,19 +3067,19 @@
       <c r="J12" s="17" t="n">
         <v>2188.25</v>
       </c>
-      <c r="K12" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" s="17" t="n">
+      <c r="K12" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="16" t="n">
         <v>2188.25</v>
       </c>
       <c r="M12" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="N12" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" s="17" t="n">
+      <c r="N12" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="16" t="n">
         <v>150000</v>
       </c>
     </row>
@@ -3169,19 +3120,19 @@
       <c r="J13" s="11" t="n">
         <v>767.8099999999999</v>
       </c>
-      <c r="K13" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" s="11" t="n">
+      <c r="K13" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="10" t="n">
         <v>767.8099999999999</v>
       </c>
       <c r="M13" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N13" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" s="11" t="n">
+      <c r="N13" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="10" t="n">
         <v>50000</v>
       </c>
     </row>
@@ -3222,19 +3173,19 @@
       <c r="J14" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="K14" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" s="17" t="n">
+      <c r="K14" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="16" t="n">
         <v>0</v>
       </c>
       <c r="M14" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="N14" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" s="17" t="n">
+      <c r="N14" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="16" t="n">
         <v>71613.56</v>
       </c>
     </row>
@@ -3275,19 +3226,19 @@
       <c r="J15" s="11" t="n">
         <v>1451.15</v>
       </c>
-      <c r="K15" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" s="11" t="n">
+      <c r="K15" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="10" t="n">
         <v>1451.15</v>
       </c>
       <c r="M15" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N15" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" s="11" t="n">
+      <c r="N15" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" s="10" t="n">
         <v>90000</v>
       </c>
     </row>
@@ -3302,7 +3253,7 @@
       </c>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>Amorós Cock de Quintanilla Consuelo Raquel / Quintanilla Quispe Teodoro</t>
+          <t xml:space="preserve">Amorós Cock de Quintanilla Consuelo Raquel / Quintanilla Quispe Teodoro </t>
         </is>
       </c>
       <c r="D16" s="15" t="inlineStr">
@@ -3328,19 +3279,19 @@
       <c r="J16" s="17" t="n">
         <v>1243.85</v>
       </c>
-      <c r="K16" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" s="17" t="n">
+      <c r="K16" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="16" t="n">
         <v>1243.85</v>
       </c>
       <c r="M16" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="N16" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" s="17" t="n">
+      <c r="N16" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" s="16" t="n">
         <v>90000</v>
       </c>
     </row>
@@ -3355,7 +3306,7 @@
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>Salas Gómez Alfredo</t>
+          <t xml:space="preserve">Salas Gómez Alfredo </t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
@@ -3381,19 +3332,19 @@
       <c r="J17" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="K17" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" s="11" t="n">
+      <c r="K17" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="10" t="n">
         <v>0</v>
       </c>
       <c r="M17" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N17" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" s="11" t="n">
+      <c r="N17" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" s="10" t="n">
         <v>50794.61</v>
       </c>
     </row>
@@ -3434,19 +3385,19 @@
       <c r="J18" s="17" t="n">
         <v>2194.34</v>
       </c>
-      <c r="K18" s="16" t="n">
+      <c r="K18" s="17" t="n">
         <v>192.48</v>
       </c>
-      <c r="L18" s="17" t="n">
+      <c r="L18" s="16" t="n">
         <v>2001.86</v>
       </c>
       <c r="M18" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="N18" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" s="17" t="n">
+      <c r="N18" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" s="16" t="n">
         <v>150417.09</v>
       </c>
     </row>
@@ -3487,19 +3438,19 @@
       <c r="J19" s="11" t="n">
         <v>2917.67</v>
       </c>
-      <c r="K19" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" s="11" t="n">
+      <c r="K19" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="10" t="n">
         <v>2917.67</v>
       </c>
       <c r="M19" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N19" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" s="11" t="n">
+      <c r="N19" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" s="10" t="n">
         <v>190000</v>
       </c>
     </row>
@@ -3540,19 +3491,19 @@
       <c r="J20" s="17" t="n">
         <v>2303.43</v>
       </c>
-      <c r="K20" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" s="17" t="n">
+      <c r="K20" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="16" t="n">
         <v>2303.43</v>
       </c>
       <c r="M20" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="N20" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" s="17" t="n">
+      <c r="N20" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" s="16" t="n">
         <v>150000</v>
       </c>
     </row>
@@ -3593,19 +3544,19 @@
       <c r="J21" s="11" t="n">
         <v>3209.44</v>
       </c>
-      <c r="K21" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" s="11" t="n">
+      <c r="K21" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="10" t="n">
         <v>3209.44</v>
       </c>
       <c r="M21" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N21" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" s="11" t="n">
+      <c r="N21" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" s="10" t="n">
         <v>220000</v>
       </c>
     </row>
@@ -3646,19 +3597,19 @@
       <c r="J22" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="K22" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" s="17" t="n">
+      <c r="K22" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="16" t="n">
         <v>0</v>
       </c>
       <c r="M22" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="N22" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" s="17" t="n">
+      <c r="N22" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" s="16" t="n">
         <v>89828.87</v>
       </c>
     </row>
@@ -3699,19 +3650,19 @@
       <c r="J23" s="11" t="n">
         <v>1458.84</v>
       </c>
-      <c r="K23" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" s="11" t="n">
+      <c r="K23" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" s="10" t="n">
         <v>1458.84</v>
       </c>
       <c r="M23" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N23" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" s="11" t="n">
+      <c r="N23" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" s="10" t="n">
         <v>100000</v>
       </c>
     </row>
@@ -3752,19 +3703,19 @@
       <c r="J24" s="17" t="n">
         <v>729.42</v>
       </c>
-      <c r="K24" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" s="17" t="n">
+      <c r="K24" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="16" t="n">
         <v>729.42</v>
       </c>
       <c r="M24" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="N24" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" s="17" t="n">
+      <c r="N24" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" s="16" t="n">
         <v>50000</v>
       </c>
     </row>
@@ -3805,19 +3756,19 @@
       <c r="J25" s="11" t="n">
         <v>1228.49</v>
       </c>
-      <c r="K25" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" s="11" t="n">
+      <c r="K25" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="10" t="n">
         <v>1228.49</v>
       </c>
       <c r="M25" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N25" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" s="11" t="n">
+      <c r="N25" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" s="10" t="n">
         <v>80000</v>
       </c>
     </row>
@@ -3858,19 +3809,19 @@
       <c r="J26" s="17" t="n">
         <v>729.42</v>
       </c>
-      <c r="K26" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" s="17" t="n">
+      <c r="K26" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="16" t="n">
         <v>729.42</v>
       </c>
       <c r="M26" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="N26" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" s="17" t="n">
+      <c r="N26" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" s="16" t="n">
         <v>50000</v>
       </c>
     </row>
@@ -3911,19 +3862,19 @@
       <c r="J27" s="11" t="n">
         <v>3086.59</v>
       </c>
-      <c r="K27" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" s="11" t="n">
+      <c r="K27" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="10" t="n">
         <v>3086.59</v>
       </c>
       <c r="M27" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N27" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" s="11" t="n">
+      <c r="N27" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" s="10" t="n">
         <v>201000</v>
       </c>
     </row>
@@ -3964,19 +3915,19 @@
       <c r="J28" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="K28" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" s="17" t="n">
+      <c r="K28" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="16" t="n">
         <v>0</v>
       </c>
       <c r="M28" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="N28" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" s="17" t="n">
+      <c r="N28" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" s="16" t="n">
         <v>222975.89</v>
       </c>
     </row>
@@ -4017,135 +3968,84 @@
       <c r="J29" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="K29" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" s="11" t="n">
+      <c r="K29" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="10" t="n">
         <v>0</v>
       </c>
       <c r="M29" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N29" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" s="11" t="n">
+      <c r="N29" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" s="10" t="n">
         <v>311337.53</v>
       </c>
     </row>
-    <row r="30" ht="19" customHeight="1">
-      <c r="A30" s="12" t="n">
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="18" t="inlineStr"/>
+      <c r="B30" s="19" t="inlineStr"/>
+      <c r="C30" s="19" t="inlineStr">
+        <is>
+          <t>TOTALES NSGPEN02 (PEN)</t>
+        </is>
+      </c>
+      <c r="D30" s="18" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="E30" s="20">
+        <f>SUM(E5:E29)</f>
         <v/>
       </c>
-      <c r="B30" s="13" t="n">
+      <c r="F30" s="20">
+        <f>SUM(F5:F29)</f>
         <v/>
       </c>
-      <c r="C30" s="14" t="inlineStr">
-        <is>
-          <t>TOTALES NSGPEN02 (PEN)</t>
-        </is>
-      </c>
-      <c r="D30" s="15" t="inlineStr">
-        <is>
-          <t>PEN</t>
-        </is>
-      </c>
-      <c r="E30" s="16" t="n">
+      <c r="G30" s="20">
+        <f>SUM(G5:G29)</f>
         <v/>
       </c>
-      <c r="F30" s="16" t="n">
+      <c r="H30" s="20">
+        <f>SUM(H5:H29)</f>
         <v/>
       </c>
-      <c r="G30" s="17" t="n">
+      <c r="I30" s="20">
+        <f>SUM(I5:I29)</f>
         <v/>
       </c>
-      <c r="H30" s="17" t="n">
+      <c r="J30" s="20">
+        <f>SUM(J5:J29)</f>
         <v/>
       </c>
-      <c r="I30" s="17" t="n">
+      <c r="K30" s="20">
+        <f>SUM(K5:K29)</f>
         <v/>
       </c>
-      <c r="J30" s="17" t="n">
+      <c r="L30" s="20">
+        <f>SUM(L5:L29)</f>
         <v/>
       </c>
-      <c r="K30" s="16" t="n">
+      <c r="M30" s="20">
+        <f>SUM(M5:M29)</f>
         <v/>
       </c>
-      <c r="L30" s="17" t="n">
+      <c r="N30" s="20">
+        <f>SUM(N5:N29)</f>
         <v/>
       </c>
-      <c r="M30" s="17" t="n">
-        <v/>
-      </c>
-      <c r="N30" s="16" t="n">
-        <v/>
-      </c>
-      <c r="O30" s="17" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="18" t="inlineStr"/>
-      <c r="B31" s="19" t="inlineStr"/>
-      <c r="C31" s="19" t="inlineStr">
-        <is>
-          <t>TOTALES NSGPEN02 (PEN)</t>
-        </is>
-      </c>
-      <c r="D31" s="18" t="inlineStr">
-        <is>
-          <t>PEN</t>
-        </is>
-      </c>
-      <c r="E31" s="20">
-        <f>SUM(E5:E30)</f>
-        <v/>
-      </c>
-      <c r="F31" s="20">
-        <f>SUM(F5:F30)</f>
-        <v/>
-      </c>
-      <c r="G31" s="20">
-        <f>SUM(G5:G30)</f>
-        <v/>
-      </c>
-      <c r="H31" s="20">
-        <f>SUM(H5:H30)</f>
-        <v/>
-      </c>
-      <c r="I31" s="20">
-        <f>SUM(I5:I30)</f>
-        <v/>
-      </c>
-      <c r="J31" s="20">
-        <f>SUM(J5:J30)</f>
-        <v/>
-      </c>
-      <c r="K31" s="20">
-        <f>SUM(K5:K30)</f>
-        <v/>
-      </c>
-      <c r="L31" s="20">
-        <f>SUM(L5:L30)</f>
-        <v/>
-      </c>
-      <c r="M31" s="20">
-        <f>SUM(M5:M30)</f>
-        <v/>
-      </c>
-      <c r="N31" s="20">
-        <f>SUM(N5:N30)</f>
-        <v/>
-      </c>
-      <c r="O31" s="20">
-        <f>SUM(O5:O30)</f>
+      <c r="O30" s="20">
+        <f>SUM(O5:O29)</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:N2"/>
-    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A2:O2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4157,10 +4057,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O78"/>
+  <dimension ref="A1:O77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
     <col width="38" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
@@ -4177,7 +4077,7 @@
     <col width="16" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
+    <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>INANDES GRUPO FINANCIERO &amp; GEEKSOFT — AUDITORÍA Y CIERRE CONTABLE</t>
@@ -4187,7 +4087,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Período: 01/01/2026 al 28/02/2026 (59 Días Base 365)  |  Fondo: NSGPEN03 (PEN)  |  Total Inversionistas: 73</t>
+          <t>Período: 01/01/2026 al 28/02/2026 (59 Días Base 365)  |  Fondo: NSGPEN03 (PEN)  |  Total Inversionistas: 72</t>
         </is>
       </c>
     </row>
@@ -4306,19 +4206,19 @@
       <c r="J5" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="K5" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" s="11" t="n">
+      <c r="K5" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="10" t="n">
         <v>0</v>
       </c>
       <c r="M5" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N5" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" s="11" t="n">
+      <c r="N5" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="10" t="n">
         <v>85046</v>
       </c>
     </row>
@@ -4359,19 +4259,19 @@
       <c r="J6" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="K6" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="17" t="n">
+      <c r="K6" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="16" t="n">
         <v>0</v>
       </c>
       <c r="M6" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="N6" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" s="17" t="n">
+      <c r="N6" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="16" t="n">
         <v>50550.48</v>
       </c>
     </row>
@@ -4412,19 +4312,19 @@
       <c r="J7" s="11" t="n">
         <v>1354.41</v>
       </c>
-      <c r="K7" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="11" t="n">
+      <c r="K7" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="10" t="n">
         <v>1354.41</v>
       </c>
       <c r="M7" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N7" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" s="11" t="n">
+      <c r="N7" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="10" t="n">
         <v>98000</v>
       </c>
     </row>
@@ -4465,19 +4365,19 @@
       <c r="J8" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="K8" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" s="17" t="n">
+      <c r="K8" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="16" t="n">
         <v>0</v>
       </c>
       <c r="M8" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="N8" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" s="17" t="n">
+      <c r="N8" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="16" t="n">
         <v>242475.92</v>
       </c>
     </row>
@@ -4518,19 +4418,19 @@
       <c r="J9" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="K9" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" s="11" t="n">
+      <c r="K9" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="10" t="n">
         <v>0</v>
       </c>
       <c r="M9" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N9" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" s="11" t="n">
+      <c r="N9" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="10" t="n">
         <v>153734.47</v>
       </c>
     </row>
@@ -4571,19 +4471,19 @@
       <c r="J10" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="K10" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" s="17" t="n">
+      <c r="K10" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="16" t="n">
         <v>0</v>
       </c>
       <c r="M10" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="N10" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" s="17" t="n">
+      <c r="N10" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="16" t="n">
         <v>255554.72</v>
       </c>
     </row>
@@ -4624,19 +4524,19 @@
       <c r="J11" s="11" t="n">
         <v>3071.24</v>
       </c>
-      <c r="K11" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" s="11" t="n">
+      <c r="K11" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="10" t="n">
         <v>3071.24</v>
       </c>
       <c r="M11" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N11" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" s="11" t="n">
+      <c r="N11" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="10" t="n">
         <v>200000</v>
       </c>
     </row>
@@ -4677,19 +4577,19 @@
       <c r="J12" s="17" t="n">
         <v>3501.21</v>
       </c>
-      <c r="K12" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" s="17" t="n">
+      <c r="K12" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="16" t="n">
         <v>3501.21</v>
       </c>
       <c r="M12" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="N12" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" s="17" t="n">
+      <c r="N12" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="16" t="n">
         <v>240000</v>
       </c>
     </row>
@@ -4730,19 +4630,19 @@
       <c r="J13" s="11" t="n">
         <v>2480.02</v>
       </c>
-      <c r="K13" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" s="11" t="n">
+      <c r="K13" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="10" t="n">
         <v>2480.02</v>
       </c>
       <c r="M13" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N13" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" s="11" t="n">
+      <c r="N13" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="10" t="n">
         <v>170000</v>
       </c>
     </row>
@@ -4783,19 +4683,19 @@
       <c r="J14" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="K14" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" s="17" t="n">
+      <c r="K14" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="16" t="n">
         <v>0</v>
       </c>
       <c r="M14" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="N14" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" s="17" t="n">
+      <c r="N14" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="16" t="n">
         <v>102299.25</v>
       </c>
     </row>
@@ -4836,19 +4736,19 @@
       <c r="J15" s="11" t="n">
         <v>1689.18</v>
       </c>
-      <c r="K15" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" s="11" t="n">
+      <c r="K15" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="10" t="n">
         <v>1689.18</v>
       </c>
       <c r="M15" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N15" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" s="11" t="n">
+      <c r="N15" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" s="10" t="n">
         <v>110000</v>
       </c>
     </row>
@@ -4889,19 +4789,19 @@
       <c r="J16" s="17" t="n">
         <v>7370.95</v>
       </c>
-      <c r="K16" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" s="17" t="n">
+      <c r="K16" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="16" t="n">
         <v>7370.95</v>
       </c>
       <c r="M16" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="N16" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" s="17" t="n">
+      <c r="N16" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" s="16" t="n">
         <v>480000</v>
       </c>
     </row>
@@ -4942,19 +4842,19 @@
       <c r="J17" s="11" t="n">
         <v>2334.14</v>
       </c>
-      <c r="K17" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" s="11" t="n">
+      <c r="K17" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="10" t="n">
         <v>2334.14</v>
       </c>
       <c r="M17" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N17" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" s="11" t="n">
+      <c r="N17" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" s="10" t="n">
         <v>160000</v>
       </c>
     </row>
@@ -4995,19 +4895,19 @@
       <c r="J18" s="17" t="n">
         <v>6910.27</v>
       </c>
-      <c r="K18" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" s="17" t="n">
+      <c r="K18" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="16" t="n">
         <v>6910.27</v>
       </c>
       <c r="M18" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="N18" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" s="17" t="n">
+      <c r="N18" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" s="16" t="n">
         <v>450000</v>
       </c>
     </row>
@@ -5048,19 +4948,19 @@
       <c r="J19" s="11" t="n">
         <v>7678.08</v>
       </c>
-      <c r="K19" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" s="11" t="n">
+      <c r="K19" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="10" t="n">
         <v>7678.08</v>
       </c>
       <c r="M19" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N19" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" s="11" t="n">
+      <c r="N19" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" s="10" t="n">
         <v>500000</v>
       </c>
     </row>
@@ -5101,19 +5001,19 @@
       <c r="J20" s="17" t="n">
         <v>1458.84</v>
       </c>
-      <c r="K20" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" s="17" t="n">
+      <c r="K20" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="16" t="n">
         <v>1458.84</v>
       </c>
       <c r="M20" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="N20" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" s="17" t="n">
+      <c r="N20" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" s="16" t="n">
         <v>100000</v>
       </c>
     </row>
@@ -5154,19 +5054,19 @@
       <c r="J21" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="K21" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" s="11" t="n">
+      <c r="K21" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="10" t="n">
         <v>0</v>
       </c>
       <c r="M21" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N21" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" s="11" t="n">
+      <c r="N21" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" s="10" t="n">
         <v>205185.34</v>
       </c>
     </row>
@@ -5207,19 +5107,19 @@
       <c r="J22" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="K22" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" s="17" t="n">
+      <c r="K22" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="16" t="n">
         <v>0</v>
       </c>
       <c r="M22" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="N22" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" s="17" t="n">
+      <c r="N22" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" s="16" t="n">
         <v>101305.27</v>
       </c>
     </row>
@@ -5260,19 +5160,19 @@
       <c r="J23" s="11" t="n">
         <v>1382.05</v>
       </c>
-      <c r="K23" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" s="11" t="n">
+      <c r="K23" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" s="10" t="n">
         <v>1382.05</v>
       </c>
       <c r="M23" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N23" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" s="11" t="n">
+      <c r="N23" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" s="10" t="n">
         <v>100000</v>
       </c>
     </row>
@@ -5313,19 +5213,19 @@
       <c r="J24" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="K24" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" s="17" t="n">
+      <c r="K24" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="16" t="n">
         <v>0</v>
       </c>
       <c r="M24" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="N24" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" s="17" t="n">
+      <c r="N24" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" s="16" t="n">
         <v>60576.25</v>
       </c>
     </row>
@@ -5366,19 +5266,19 @@
       <c r="J25" s="11" t="n">
         <v>468.49</v>
       </c>
-      <c r="K25" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" s="11" t="n">
+      <c r="K25" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="10" t="n">
         <v>468.49</v>
       </c>
       <c r="M25" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N25" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" s="11" t="n">
+      <c r="N25" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" s="10" t="n">
         <v>50000</v>
       </c>
     </row>
@@ -5419,19 +5319,19 @@
       <c r="J26" s="17" t="n">
         <v>913.5599999999999</v>
       </c>
-      <c r="K26" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" s="17" t="n">
+      <c r="K26" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="16" t="n">
         <v>913.5599999999999</v>
       </c>
       <c r="M26" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="N26" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" s="17" t="n">
+      <c r="N26" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" s="16" t="n">
         <v>100000</v>
       </c>
     </row>
@@ -5472,19 +5372,19 @@
       <c r="J27" s="11" t="n">
         <v>1474.19</v>
       </c>
-      <c r="K27" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" s="11" t="n">
+      <c r="K27" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="10" t="n">
         <v>1474.19</v>
       </c>
       <c r="M27" s="11" t="n">
         <v>20000</v>
       </c>
-      <c r="N27" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" s="11" t="n">
+      <c r="N27" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" s="10" t="n">
         <v>100000</v>
       </c>
     </row>
@@ -5525,19 +5425,19 @@
       <c r="J28" s="17" t="n">
         <v>1382.05</v>
       </c>
-      <c r="K28" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" s="17" t="n">
+      <c r="K28" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="16" t="n">
         <v>1382.05</v>
       </c>
       <c r="M28" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="N28" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" s="17" t="n">
+      <c r="N28" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" s="16" t="n">
         <v>100000</v>
       </c>
     </row>
@@ -5578,19 +5478,19 @@
       <c r="J29" s="11" t="n">
         <v>1535.62</v>
       </c>
-      <c r="K29" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" s="11" t="n">
+      <c r="K29" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="10" t="n">
         <v>1535.62</v>
       </c>
       <c r="M29" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N29" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" s="11" t="n">
+      <c r="N29" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" s="10" t="n">
         <v>100000</v>
       </c>
     </row>
@@ -5631,19 +5531,19 @@
       <c r="J30" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="K30" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" s="17" t="n">
+      <c r="K30" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" s="16" t="n">
         <v>0</v>
       </c>
       <c r="M30" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="N30" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" s="17" t="n">
+      <c r="N30" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" s="16" t="n">
         <v>50333.8</v>
       </c>
     </row>
@@ -5684,19 +5584,19 @@
       <c r="J31" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="K31" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" s="11" t="n">
+      <c r="K31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" s="10" t="n">
         <v>0</v>
       </c>
       <c r="M31" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N31" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" s="11" t="n">
+      <c r="N31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" s="10" t="n">
         <v>323186.94</v>
       </c>
     </row>
@@ -5737,19 +5637,19 @@
       <c r="J32" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="K32" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" s="17" t="n">
+      <c r="K32" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="16" t="n">
         <v>0</v>
       </c>
       <c r="M32" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="N32" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" s="17" t="n">
+      <c r="N32" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" s="16" t="n">
         <v>100642.87</v>
       </c>
     </row>
@@ -5790,19 +5690,19 @@
       <c r="J33" s="11" t="n">
         <v>5439.73</v>
       </c>
-      <c r="K33" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" s="11" t="n">
+      <c r="K33" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="10" t="n">
         <v>5439.73</v>
       </c>
       <c r="M33" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N33" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" s="11" t="n">
+      <c r="N33" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" s="10" t="n">
         <v>550000</v>
       </c>
     </row>
@@ -5817,7 +5717,7 @@
       </c>
       <c r="C34" s="14" t="inlineStr">
         <is>
-          <t>Yagua Padilla Tirzo</t>
+          <t xml:space="preserve">Yagua Padilla Tirzo </t>
         </is>
       </c>
       <c r="D34" s="15" t="inlineStr">
@@ -5843,19 +5743,19 @@
       <c r="J34" s="17" t="n">
         <v>6526.37</v>
       </c>
-      <c r="K34" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" s="17" t="n">
+      <c r="K34" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="16" t="n">
         <v>6526.37</v>
       </c>
       <c r="M34" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="N34" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" s="17" t="n">
+      <c r="N34" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" s="16" t="n">
         <v>500000</v>
       </c>
     </row>
@@ -5896,19 +5796,19 @@
       <c r="J35" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="K35" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" s="11" t="n">
+      <c r="K35" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="10" t="n">
         <v>0</v>
       </c>
       <c r="M35" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N35" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" s="11" t="n">
+      <c r="N35" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" s="10" t="n">
         <v>69461.52</v>
       </c>
     </row>
@@ -5949,19 +5849,19 @@
       <c r="J36" s="17" t="n">
         <v>729.42</v>
       </c>
-      <c r="K36" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" s="17" t="n">
+      <c r="K36" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="16" t="n">
         <v>729.42</v>
       </c>
       <c r="M36" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="N36" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" s="17" t="n">
+      <c r="N36" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" s="16" t="n">
         <v>50000</v>
       </c>
     </row>
@@ -6002,19 +5902,19 @@
       <c r="J37" s="11" t="n">
         <v>370.89</v>
       </c>
-      <c r="K37" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" s="11" t="n">
+      <c r="K37" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" s="10" t="n">
         <v>370.89</v>
       </c>
       <c r="M37" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N37" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O37" s="11" t="n">
+      <c r="N37" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" s="10" t="n">
         <v>150000</v>
       </c>
     </row>
@@ -6055,19 +5955,19 @@
       <c r="J38" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="K38" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" s="17" t="n">
+      <c r="K38" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" s="16" t="n">
         <v>0</v>
       </c>
       <c r="M38" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="N38" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" s="17" t="n">
+      <c r="N38" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" s="16" t="n">
         <v>138895.74</v>
       </c>
     </row>
@@ -6108,19 +6008,19 @@
       <c r="J39" s="11" t="n">
         <v>2764.11</v>
       </c>
-      <c r="K39" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" s="11" t="n">
+      <c r="K39" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" s="10" t="n">
         <v>2764.11</v>
       </c>
       <c r="M39" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N39" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" s="11" t="n">
+      <c r="N39" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" s="10" t="n">
         <v>200000</v>
       </c>
     </row>
@@ -6161,19 +6061,19 @@
       <c r="J40" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="K40" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L40" s="17" t="n">
+      <c r="K40" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="16" t="n">
         <v>0</v>
       </c>
       <c r="M40" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="N40" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O40" s="17" t="n">
+      <c r="N40" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" s="16" t="n">
         <v>80098.89999999999</v>
       </c>
     </row>
@@ -6214,19 +6114,19 @@
       <c r="J41" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="K41" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" s="11" t="n">
+      <c r="K41" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" s="10" t="n">
         <v>0</v>
       </c>
       <c r="M41" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N41" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O41" s="11" t="n">
+      <c r="N41" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" s="10" t="n">
         <v>53419.38</v>
       </c>
     </row>
@@ -6267,19 +6167,19 @@
       <c r="J42" s="17" t="n">
         <v>859.95</v>
       </c>
-      <c r="K42" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L42" s="17" t="n">
+      <c r="K42" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" s="16" t="n">
         <v>859.95</v>
       </c>
       <c r="M42" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="N42" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O42" s="17" t="n">
+      <c r="N42" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" s="16" t="n">
         <v>56000</v>
       </c>
     </row>
@@ -6320,19 +6220,19 @@
       <c r="J43" s="11" t="n">
         <v>1458.84</v>
       </c>
-      <c r="K43" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" s="11" t="n">
+      <c r="K43" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" s="10" t="n">
         <v>1458.84</v>
       </c>
       <c r="M43" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N43" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O43" s="11" t="n">
+      <c r="N43" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" s="10" t="n">
         <v>100000</v>
       </c>
     </row>
@@ -6373,19 +6273,19 @@
       <c r="J44" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="K44" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" s="17" t="n">
+      <c r="K44" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" s="16" t="n">
         <v>0</v>
       </c>
       <c r="M44" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="N44" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O44" s="17" t="n">
+      <c r="N44" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" s="16" t="n">
         <v>692281.1</v>
       </c>
     </row>
@@ -6400,7 +6300,7 @@
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>Navarrete  Josefina</t>
+          <t xml:space="preserve">Navarrete  Josefina </t>
         </is>
       </c>
       <c r="D45" s="9" t="inlineStr">
@@ -6426,19 +6326,19 @@
       <c r="J45" s="11" t="n">
         <v>1023.24</v>
       </c>
-      <c r="K45" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" s="11" t="n">
+      <c r="K45" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" s="10" t="n">
         <v>1023.24</v>
       </c>
       <c r="M45" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N45" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O45" s="11" t="n">
+      <c r="N45" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" s="10" t="n">
         <v>70140.39</v>
       </c>
     </row>
@@ -6479,19 +6379,19 @@
       <c r="J46" s="17" t="n">
         <v>8868.18</v>
       </c>
-      <c r="K46" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" s="17" t="n">
+      <c r="K46" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" s="16" t="n">
         <v>8868.18</v>
       </c>
       <c r="M46" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="N46" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O46" s="17" t="n">
+      <c r="N46" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" s="16" t="n">
         <v>550000</v>
       </c>
     </row>
@@ -6532,19 +6432,19 @@
       <c r="J47" s="11" t="n">
         <v>1289.92</v>
       </c>
-      <c r="K47" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L47" s="11" t="n">
+      <c r="K47" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" s="10" t="n">
         <v>1289.92</v>
       </c>
       <c r="M47" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N47" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O47" s="11" t="n">
+      <c r="N47" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" s="10" t="n">
         <v>80000</v>
       </c>
     </row>
@@ -6559,7 +6459,7 @@
       </c>
       <c r="C48" s="14" t="inlineStr">
         <is>
-          <t>Aravena Elías Rodrigo</t>
+          <t xml:space="preserve">Aravena Elías Rodrigo </t>
         </is>
       </c>
       <c r="D48" s="15" t="inlineStr">
@@ -6585,19 +6485,19 @@
       <c r="J48" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="K48" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" s="17" t="n">
+      <c r="K48" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" s="16" t="n">
         <v>0</v>
       </c>
       <c r="M48" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="N48" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O48" s="17" t="n">
+      <c r="N48" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" s="16" t="n">
         <v>97675.19</v>
       </c>
     </row>
@@ -6638,19 +6538,19 @@
       <c r="J49" s="11" t="n">
         <v>2764.11</v>
       </c>
-      <c r="K49" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" s="11" t="n">
+      <c r="K49" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" s="10" t="n">
         <v>2764.11</v>
       </c>
       <c r="M49" s="11" t="n">
         <v>200000</v>
       </c>
-      <c r="N49" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O49" s="11" t="n">
+      <c r="N49" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6691,19 +6591,19 @@
       <c r="J50" s="17" t="n">
         <v>3071.24</v>
       </c>
-      <c r="K50" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L50" s="17" t="n">
+      <c r="K50" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" s="16" t="n">
         <v>3071.24</v>
       </c>
       <c r="M50" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="N50" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O50" s="17" t="n">
+      <c r="N50" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" s="16" t="n">
         <v>200000</v>
       </c>
     </row>
@@ -6718,7 +6618,7 @@
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>Anicama Alzamora Carlos Alex / Yataco Castro de Anicama Doris</t>
+          <t xml:space="preserve">Anicama Alzamora Carlos Alex / Yataco Castro de Anicama Doris </t>
         </is>
       </c>
       <c r="D51" s="9" t="inlineStr">
@@ -6744,19 +6644,19 @@
       <c r="J51" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="K51" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L51" s="11" t="n">
+      <c r="K51" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" s="10" t="n">
         <v>0</v>
       </c>
       <c r="M51" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N51" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O51" s="11" t="n">
+      <c r="N51" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" s="10" t="n">
         <v>247133.14</v>
       </c>
     </row>
@@ -6797,19 +6697,19 @@
       <c r="J52" s="17" t="n">
         <v>744</v>
       </c>
-      <c r="K52" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L52" s="17" t="n">
+      <c r="K52" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" s="16" t="n">
         <v>744</v>
       </c>
       <c r="M52" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="N52" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O52" s="17" t="n">
+      <c r="N52" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" s="16" t="n">
         <v>51000</v>
       </c>
     </row>
@@ -6850,19 +6750,19 @@
       <c r="J53" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="K53" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L53" s="11" t="n">
+      <c r="K53" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" s="10" t="n">
         <v>0</v>
       </c>
       <c r="M53" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N53" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O53" s="11" t="n">
+      <c r="N53" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" s="10" t="n">
         <v>319412.69</v>
       </c>
     </row>
@@ -6877,7 +6777,7 @@
       </c>
       <c r="C54" s="14" t="inlineStr">
         <is>
-          <t>López Cabrera Guillermina</t>
+          <t xml:space="preserve">López Cabrera Guillermina </t>
         </is>
       </c>
       <c r="D54" s="15" t="inlineStr">
@@ -6903,19 +6803,19 @@
       <c r="J54" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="K54" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" s="17" t="n">
+      <c r="K54" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" s="16" t="n">
         <v>0</v>
       </c>
       <c r="M54" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="N54" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O54" s="17" t="n">
+      <c r="N54" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" s="16" t="n">
         <v>79119.32000000001</v>
       </c>
     </row>
@@ -6956,19 +6856,19 @@
       <c r="J55" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="K55" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L55" s="11" t="n">
+      <c r="K55" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" s="10" t="n">
         <v>0</v>
       </c>
       <c r="M55" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N55" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O55" s="11" t="n">
+      <c r="N55" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" s="10" t="n">
         <v>35551.56</v>
       </c>
     </row>
@@ -7009,19 +6909,19 @@
       <c r="J56" s="17" t="n">
         <v>967.4400000000001</v>
       </c>
-      <c r="K56" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L56" s="17" t="n">
+      <c r="K56" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" s="16" t="n">
         <v>967.4400000000001</v>
       </c>
       <c r="M56" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="N56" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O56" s="17" t="n">
+      <c r="N56" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" s="16" t="n">
         <v>70000</v>
       </c>
     </row>
@@ -7062,19 +6962,19 @@
       <c r="J57" s="11" t="n">
         <v>5105.93</v>
       </c>
-      <c r="K57" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L57" s="11" t="n">
+      <c r="K57" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" s="10" t="n">
         <v>5105.93</v>
       </c>
       <c r="M57" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N57" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O57" s="11" t="n">
+      <c r="N57" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" s="10" t="n">
         <v>350000</v>
       </c>
     </row>
@@ -7115,19 +7015,19 @@
       <c r="J58" s="17" t="n">
         <v>1021.18</v>
       </c>
-      <c r="K58" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L58" s="17" t="n">
+      <c r="K58" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" s="16" t="n">
         <v>1021.18</v>
       </c>
       <c r="M58" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="N58" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O58" s="17" t="n">
+      <c r="N58" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" s="16" t="n">
         <v>70000</v>
       </c>
     </row>
@@ -7135,8 +7035,10 @@
       <c r="A59" s="6" t="n">
         <v>55</v>
       </c>
-      <c r="B59" s="7" t="n">
-        <v/>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>NSGPEN03-017.20160101.20251231</t>
+        </is>
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
@@ -7166,19 +7068,19 @@
       <c r="J59" s="11" t="n">
         <v>2480.02</v>
       </c>
-      <c r="K59" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L59" s="11" t="n">
+      <c r="K59" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" s="10" t="n">
         <v>2480.02</v>
       </c>
       <c r="M59" s="11" t="n">
         <v>190000</v>
       </c>
-      <c r="N59" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O59" s="11" t="n">
+      <c r="N59" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7219,19 +7121,19 @@
       <c r="J60" s="17" t="n">
         <v>2188.25</v>
       </c>
-      <c r="K60" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L60" s="17" t="n">
+      <c r="K60" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" s="16" t="n">
         <v>2188.25</v>
       </c>
       <c r="M60" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="N60" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O60" s="17" t="n">
+      <c r="N60" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" s="16" t="n">
         <v>150000</v>
       </c>
     </row>
@@ -7272,19 +7174,19 @@
       <c r="J61" s="11" t="n">
         <v>1305.27</v>
       </c>
-      <c r="K61" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L61" s="11" t="n">
+      <c r="K61" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" s="10" t="n">
         <v>1305.27</v>
       </c>
       <c r="M61" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N61" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O61" s="11" t="n">
+      <c r="N61" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O61" s="10" t="n">
         <v>100000</v>
       </c>
     </row>
@@ -7325,19 +7227,19 @@
       <c r="J62" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="K62" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L62" s="17" t="n">
+      <c r="K62" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" s="16" t="n">
         <v>0</v>
       </c>
       <c r="M62" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="N62" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O62" s="17" t="n">
+      <c r="N62" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" s="16" t="n">
         <v>272099.51</v>
       </c>
     </row>
@@ -7352,7 +7254,7 @@
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
-          <t>López Palomino Vicenta</t>
+          <t xml:space="preserve">López Palomino Vicenta </t>
         </is>
       </c>
       <c r="D63" s="9" t="inlineStr">
@@ -7378,19 +7280,19 @@
       <c r="J63" s="11" t="n">
         <v>1385.9</v>
       </c>
-      <c r="K63" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L63" s="11" t="n">
+      <c r="K63" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" s="10" t="n">
         <v>1385.9</v>
       </c>
       <c r="M63" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N63" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O63" s="11" t="n">
+      <c r="N63" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" s="10" t="n">
         <v>95000</v>
       </c>
     </row>
@@ -7405,7 +7307,7 @@
       </c>
       <c r="C64" s="14" t="inlineStr">
         <is>
-          <t>Castillo Taipe Ayaze</t>
+          <t xml:space="preserve">Castillo Taipe Ayaze </t>
         </is>
       </c>
       <c r="D64" s="15" t="inlineStr">
@@ -7431,19 +7333,19 @@
       <c r="J64" s="17" t="n">
         <v>729.42</v>
       </c>
-      <c r="K64" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L64" s="17" t="n">
+      <c r="K64" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" s="16" t="n">
         <v>729.42</v>
       </c>
       <c r="M64" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="N64" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O64" s="17" t="n">
+      <c r="N64" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O64" s="16" t="n">
         <v>50000</v>
       </c>
     </row>
@@ -7484,19 +7386,19 @@
       <c r="J65" s="11" t="n">
         <v>4560.78</v>
       </c>
-      <c r="K65" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L65" s="11" t="n">
+      <c r="K65" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" s="10" t="n">
         <v>4560.78</v>
       </c>
       <c r="M65" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N65" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O65" s="11" t="n">
+      <c r="N65" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O65" s="10" t="n">
         <v>330000</v>
       </c>
     </row>
@@ -7537,19 +7439,19 @@
       <c r="J66" s="17" t="n">
         <v>2188.25</v>
       </c>
-      <c r="K66" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L66" s="17" t="n">
+      <c r="K66" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" s="16" t="n">
         <v>2188.25</v>
       </c>
       <c r="M66" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="N66" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O66" s="17" t="n">
+      <c r="N66" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O66" s="16" t="n">
         <v>150000</v>
       </c>
     </row>
@@ -7590,19 +7492,19 @@
       <c r="J67" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="K67" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L67" s="11" t="n">
+      <c r="K67" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" s="10" t="n">
         <v>0</v>
       </c>
       <c r="M67" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N67" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O67" s="11" t="n">
+      <c r="N67" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O67" s="10" t="n">
         <v>163539.28</v>
       </c>
     </row>
@@ -7617,7 +7519,7 @@
       </c>
       <c r="C68" s="14" t="inlineStr">
         <is>
-          <t>Salas Gómez Alfredo</t>
+          <t xml:space="preserve">Salas Gómez Alfredo </t>
         </is>
       </c>
       <c r="D68" s="15" t="inlineStr">
@@ -7643,19 +7545,19 @@
       <c r="J68" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="K68" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L68" s="17" t="n">
+      <c r="K68" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" s="16" t="n">
         <v>0</v>
       </c>
       <c r="M68" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="N68" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O68" s="17" t="n">
+      <c r="N68" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O68" s="16" t="n">
         <v>161970.04</v>
       </c>
     </row>
@@ -7696,19 +7598,19 @@
       <c r="J69" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="K69" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L69" s="11" t="n">
+      <c r="K69" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" s="10" t="n">
         <v>0</v>
       </c>
       <c r="M69" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N69" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O69" s="11" t="n">
+      <c r="N69" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O69" s="10" t="n">
         <v>107009.06</v>
       </c>
     </row>
@@ -7749,19 +7651,19 @@
       <c r="J70" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="K70" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L70" s="17" t="n">
+      <c r="K70" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" s="16" t="n">
         <v>0</v>
       </c>
       <c r="M70" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="N70" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O70" s="17" t="n">
+      <c r="N70" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O70" s="16" t="n">
         <v>204078.4</v>
       </c>
     </row>
@@ -7802,19 +7704,19 @@
       <c r="J71" s="11" t="n">
         <v>7294.18</v>
       </c>
-      <c r="K71" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L71" s="11" t="n">
+      <c r="K71" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" s="10" t="n">
         <v>7294.18</v>
       </c>
       <c r="M71" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N71" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O71" s="11" t="n">
+      <c r="N71" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O71" s="10" t="n">
         <v>500000</v>
       </c>
     </row>
@@ -7855,19 +7757,19 @@
       <c r="J72" s="17" t="n">
         <v>1458.84</v>
       </c>
-      <c r="K72" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L72" s="17" t="n">
+      <c r="K72" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" s="16" t="n">
         <v>1458.84</v>
       </c>
       <c r="M72" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="N72" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O72" s="17" t="n">
+      <c r="N72" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O72" s="16" t="n">
         <v>100000</v>
       </c>
     </row>
@@ -7882,7 +7784,7 @@
       </c>
       <c r="C73" s="8" t="inlineStr">
         <is>
-          <t>Jarufe Medina Rufino</t>
+          <t xml:space="preserve">Jarufe Medina Rufino </t>
         </is>
       </c>
       <c r="D73" s="9" t="inlineStr">
@@ -7908,19 +7810,19 @@
       <c r="J73" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="K73" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L73" s="11" t="n">
+      <c r="K73" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" s="10" t="n">
         <v>0</v>
       </c>
       <c r="M73" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N73" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O73" s="11" t="n">
+      <c r="N73" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O73" s="10" t="n">
         <v>214863.07</v>
       </c>
     </row>
@@ -7961,19 +7863,19 @@
       <c r="J74" s="17" t="n">
         <v>1535.62</v>
       </c>
-      <c r="K74" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L74" s="17" t="n">
+      <c r="K74" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" s="16" t="n">
         <v>1535.62</v>
       </c>
       <c r="M74" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="N74" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O74" s="17" t="n">
+      <c r="N74" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O74" s="16" t="n">
         <v>100000</v>
       </c>
     </row>
@@ -8014,19 +7916,19 @@
       <c r="J75" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="K75" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L75" s="11" t="n">
+      <c r="K75" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" s="10" t="n">
         <v>0</v>
       </c>
       <c r="M75" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N75" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O75" s="11" t="n">
+      <c r="N75" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O75" s="10" t="n">
         <v>101305.27</v>
       </c>
     </row>
@@ -8067,135 +7969,84 @@
       <c r="J76" s="17" t="n">
         <v>691.03</v>
       </c>
-      <c r="K76" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L76" s="17" t="n">
+      <c r="K76" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" s="16" t="n">
         <v>691.03</v>
       </c>
       <c r="M76" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="N76" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O76" s="17" t="n">
+      <c r="N76" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O76" s="16" t="n">
         <v>50000</v>
       </c>
     </row>
-    <row r="77" ht="19" customHeight="1">
-      <c r="A77" s="6" t="n">
+    <row r="77" ht="22" customHeight="1">
+      <c r="A77" s="18" t="inlineStr"/>
+      <c r="B77" s="19" t="inlineStr"/>
+      <c r="C77" s="19" t="inlineStr">
+        <is>
+          <t>TOTALES NSGPEN03 (PEN)</t>
+        </is>
+      </c>
+      <c r="D77" s="18" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="E77" s="20">
+        <f>SUM(E5:E76)</f>
         <v/>
       </c>
-      <c r="B77" s="7" t="n">
+      <c r="F77" s="20">
+        <f>SUM(F5:F76)</f>
         <v/>
       </c>
-      <c r="C77" s="8" t="inlineStr">
-        <is>
-          <t>TOTALES NSGPEN03 (PEN)</t>
-        </is>
-      </c>
-      <c r="D77" s="9" t="inlineStr">
-        <is>
-          <t>PEN</t>
-        </is>
-      </c>
-      <c r="E77" s="10" t="n">
+      <c r="G77" s="20">
+        <f>SUM(G5:G76)</f>
         <v/>
       </c>
-      <c r="F77" s="10" t="n">
+      <c r="H77" s="20">
+        <f>SUM(H5:H76)</f>
         <v/>
       </c>
-      <c r="G77" s="11" t="n">
+      <c r="I77" s="20">
+        <f>SUM(I5:I76)</f>
         <v/>
       </c>
-      <c r="H77" s="11" t="n">
+      <c r="J77" s="20">
+        <f>SUM(J5:J76)</f>
         <v/>
       </c>
-      <c r="I77" s="11" t="n">
+      <c r="K77" s="20">
+        <f>SUM(K5:K76)</f>
         <v/>
       </c>
-      <c r="J77" s="11" t="n">
+      <c r="L77" s="20">
+        <f>SUM(L5:L76)</f>
         <v/>
       </c>
-      <c r="K77" s="10" t="n">
+      <c r="M77" s="20">
+        <f>SUM(M5:M76)</f>
         <v/>
       </c>
-      <c r="L77" s="11" t="n">
+      <c r="N77" s="20">
+        <f>SUM(N5:N76)</f>
         <v/>
       </c>
-      <c r="M77" s="11" t="n">
-        <v/>
-      </c>
-      <c r="N77" s="10" t="n">
-        <v/>
-      </c>
-      <c r="O77" s="11" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="78" ht="22" customHeight="1">
-      <c r="A78" s="18" t="inlineStr"/>
-      <c r="B78" s="19" t="inlineStr"/>
-      <c r="C78" s="19" t="inlineStr">
-        <is>
-          <t>TOTALES NSGPEN03 (PEN)</t>
-        </is>
-      </c>
-      <c r="D78" s="18" t="inlineStr">
-        <is>
-          <t>PEN</t>
-        </is>
-      </c>
-      <c r="E78" s="20">
-        <f>SUM(E5:E77)</f>
-        <v/>
-      </c>
-      <c r="F78" s="20">
-        <f>SUM(F5:F77)</f>
-        <v/>
-      </c>
-      <c r="G78" s="20">
-        <f>SUM(G5:G77)</f>
-        <v/>
-      </c>
-      <c r="H78" s="20">
-        <f>SUM(H5:H77)</f>
-        <v/>
-      </c>
-      <c r="I78" s="20">
-        <f>SUM(I5:I77)</f>
-        <v/>
-      </c>
-      <c r="J78" s="20">
-        <f>SUM(J5:J77)</f>
-        <v/>
-      </c>
-      <c r="K78" s="20">
-        <f>SUM(K5:K77)</f>
-        <v/>
-      </c>
-      <c r="L78" s="20">
-        <f>SUM(L5:L77)</f>
-        <v/>
-      </c>
-      <c r="M78" s="20">
-        <f>SUM(M5:M77)</f>
-        <v/>
-      </c>
-      <c r="N78" s="20">
-        <f>SUM(N5:N77)</f>
-        <v/>
-      </c>
-      <c r="O78" s="20">
-        <f>SUM(O5:O77)</f>
+      <c r="O77" s="20">
+        <f>SUM(O5:O76)</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:N2"/>
-    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A2:O2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8207,10 +8058,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O15"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
     <col width="38" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
@@ -8227,7 +8078,7 @@
     <col width="16" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
+    <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>INANDES GRUPO FINANCIERO &amp; GEEKSOFT — AUDITORÍA Y CIERRE CONTABLE</t>
@@ -8237,7 +8088,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Período: 01/01/2026 al 28/02/2026 (59 Días Base 365)  |  Fondo: NSGUSD01 (USD)  |  Total Inversionistas: 10</t>
+          <t>Período: 01/01/2026 al 28/02/2026 (59 Días Base 365)  |  Fondo: NSGUSD01 (USD)  |  Total Inversionistas: 9</t>
         </is>
       </c>
     </row>
@@ -8330,7 +8181,7 @@
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>Peña Jimenez Pedro</t>
+          <t xml:space="preserve">Peña Jimenez Pedro </t>
         </is>
       </c>
       <c r="D5" s="9" t="inlineStr">
@@ -8356,19 +8207,19 @@
       <c r="J5" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="K5" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" s="11" t="n">
+      <c r="K5" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="10" t="n">
         <v>0</v>
       </c>
       <c r="M5" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N5" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" s="11" t="n">
+      <c r="N5" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="10" t="n">
         <v>73680.8</v>
       </c>
     </row>
@@ -8409,19 +8260,19 @@
       <c r="J6" s="17" t="n">
         <v>391.58</v>
       </c>
-      <c r="K6" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="17" t="n">
+      <c r="K6" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="16" t="n">
         <v>391.58</v>
       </c>
       <c r="M6" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="N6" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" s="17" t="n">
+      <c r="N6" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="16" t="n">
         <v>30000</v>
       </c>
     </row>
@@ -8462,19 +8313,19 @@
       <c r="J7" s="11" t="n">
         <v>1168.22</v>
       </c>
-      <c r="K7" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="11" t="n">
+      <c r="K7" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="10" t="n">
         <v>1168.22</v>
       </c>
       <c r="M7" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N7" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" s="11" t="n">
+      <c r="N7" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="10" t="n">
         <v>89500</v>
       </c>
     </row>
@@ -8489,7 +8340,7 @@
       </c>
       <c r="C8" s="14" t="inlineStr">
         <is>
-          <t>Chávez Carbajal Juan Carlos / Caycho Carbajal Milena</t>
+          <t xml:space="preserve">Chávez Carbajal Juan Carlos / Caycho Carbajal Milena </t>
         </is>
       </c>
       <c r="D8" s="15" t="inlineStr">
@@ -8515,19 +8366,19 @@
       <c r="J8" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="K8" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" s="17" t="n">
+      <c r="K8" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="16" t="n">
         <v>0</v>
       </c>
       <c r="M8" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="N8" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" s="17" t="n">
+      <c r="N8" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="16" t="n">
         <v>56470.21</v>
       </c>
     </row>
@@ -8568,19 +8419,19 @@
       <c r="J9" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="K9" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" s="11" t="n">
+      <c r="K9" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="10" t="n">
         <v>0</v>
       </c>
       <c r="M9" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N9" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" s="11" t="n">
+      <c r="N9" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="10" t="n">
         <v>81566.06</v>
       </c>
     </row>
@@ -8621,19 +8472,19 @@
       <c r="J10" s="17" t="n">
         <v>587.38</v>
       </c>
-      <c r="K10" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" s="17" t="n">
+      <c r="K10" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="16" t="n">
         <v>587.38</v>
       </c>
       <c r="M10" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="N10" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" s="17" t="n">
+      <c r="N10" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="16" t="n">
         <v>45000</v>
       </c>
     </row>
@@ -8648,7 +8499,7 @@
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>Xiangyan  Tao</t>
+          <t xml:space="preserve">Xiangyan  Tao </t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
@@ -8674,19 +8525,19 @@
       <c r="J11" s="11" t="n">
         <v>1406.38</v>
       </c>
-      <c r="K11" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" s="11" t="n">
+      <c r="K11" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="10" t="n">
         <v>1406.38</v>
       </c>
       <c r="M11" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N11" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" s="11" t="n">
+      <c r="N11" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="10" t="n">
         <v>107745.92</v>
       </c>
     </row>
@@ -8694,8 +8545,10 @@
       <c r="A12" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="13" t="n">
-        <v/>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>NSGUSD01-037.20160101.20251231</t>
+        </is>
       </c>
       <c r="C12" s="14" t="inlineStr">
         <is>
@@ -8725,19 +8578,19 @@
       <c r="J12" s="17" t="n">
         <v>783.16</v>
       </c>
-      <c r="K12" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" s="17" t="n">
+      <c r="K12" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="16" t="n">
         <v>783.16</v>
       </c>
       <c r="M12" s="17" t="n">
         <v>60000</v>
       </c>
-      <c r="N12" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" s="17" t="n">
+      <c r="N12" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8778,135 +8631,84 @@
       <c r="J13" s="11" t="n">
         <v>1044.22</v>
       </c>
-      <c r="K13" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" s="11" t="n">
+      <c r="K13" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="10" t="n">
         <v>1044.22</v>
       </c>
       <c r="M13" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N13" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" s="11" t="n">
+      <c r="N13" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="10" t="n">
         <v>80000</v>
       </c>
     </row>
-    <row r="14" ht="19" customHeight="1">
-      <c r="A14" s="12" t="n">
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="18" t="inlineStr"/>
+      <c r="B14" s="19" t="inlineStr"/>
+      <c r="C14" s="19" t="inlineStr">
+        <is>
+          <t>TOTALES NSGUSD01 (USD)</t>
+        </is>
+      </c>
+      <c r="D14" s="18" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E14" s="20">
+        <f>SUM(E5:E13)</f>
         <v/>
       </c>
-      <c r="B14" s="13" t="n">
+      <c r="F14" s="20">
+        <f>SUM(F5:F13)</f>
         <v/>
       </c>
-      <c r="C14" s="14" t="inlineStr">
-        <is>
-          <t>TOTALES NSGUSD01 (USD)</t>
-        </is>
-      </c>
-      <c r="D14" s="15" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="E14" s="16" t="n">
+      <c r="G14" s="20">
+        <f>SUM(G5:G13)</f>
         <v/>
       </c>
-      <c r="F14" s="16" t="n">
+      <c r="H14" s="20">
+        <f>SUM(H5:H13)</f>
         <v/>
       </c>
-      <c r="G14" s="17" t="n">
+      <c r="I14" s="20">
+        <f>SUM(I5:I13)</f>
         <v/>
       </c>
-      <c r="H14" s="17" t="n">
+      <c r="J14" s="20">
+        <f>SUM(J5:J13)</f>
         <v/>
       </c>
-      <c r="I14" s="17" t="n">
+      <c r="K14" s="20">
+        <f>SUM(K5:K13)</f>
         <v/>
       </c>
-      <c r="J14" s="17" t="n">
+      <c r="L14" s="20">
+        <f>SUM(L5:L13)</f>
         <v/>
       </c>
-      <c r="K14" s="16" t="n">
+      <c r="M14" s="20">
+        <f>SUM(M5:M13)</f>
         <v/>
       </c>
-      <c r="L14" s="17" t="n">
+      <c r="N14" s="20">
+        <f>SUM(N5:N13)</f>
         <v/>
       </c>
-      <c r="M14" s="17" t="n">
-        <v/>
-      </c>
-      <c r="N14" s="16" t="n">
-        <v/>
-      </c>
-      <c r="O14" s="17" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="18" t="inlineStr"/>
-      <c r="B15" s="19" t="inlineStr"/>
-      <c r="C15" s="19" t="inlineStr">
-        <is>
-          <t>TOTALES NSGUSD01 (USD)</t>
-        </is>
-      </c>
-      <c r="D15" s="18" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="E15" s="20">
-        <f>SUM(E5:E14)</f>
-        <v/>
-      </c>
-      <c r="F15" s="20">
-        <f>SUM(F5:F14)</f>
-        <v/>
-      </c>
-      <c r="G15" s="20">
-        <f>SUM(G5:G14)</f>
-        <v/>
-      </c>
-      <c r="H15" s="20">
-        <f>SUM(H5:H14)</f>
-        <v/>
-      </c>
-      <c r="I15" s="20">
-        <f>SUM(I5:I14)</f>
-        <v/>
-      </c>
-      <c r="J15" s="20">
-        <f>SUM(J5:J14)</f>
-        <v/>
-      </c>
-      <c r="K15" s="20">
-        <f>SUM(K5:K14)</f>
-        <v/>
-      </c>
-      <c r="L15" s="20">
-        <f>SUM(L5:L14)</f>
-        <v/>
-      </c>
-      <c r="M15" s="20">
-        <f>SUM(M5:M14)</f>
-        <v/>
-      </c>
-      <c r="N15" s="20">
-        <f>SUM(N5:N14)</f>
-        <v/>
-      </c>
-      <c r="O15" s="20">
-        <f>SUM(O5:O14)</f>
+      <c r="O14" s="20">
+        <f>SUM(O5:O13)</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:N2"/>
-    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A2:O2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8918,10 +8720,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O51"/>
+  <dimension ref="A1:O50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
     <col width="38" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
@@ -8938,7 +8740,7 @@
     <col width="16" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
+    <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>INANDES GRUPO FINANCIERO &amp; GEEKSOFT — AUDITORÍA Y CIERRE CONTABLE</t>
@@ -8948,7 +8750,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Período: 01/01/2026 al 28/02/2026 (59 Días Base 365)  |  Fondo: NSGUSD02 (USD)  |  Total Inversionistas: 46</t>
+          <t>Período: 01/01/2026 al 28/02/2026 (59 Días Base 365)  |  Fondo: NSGUSD02 (USD)  |  Total Inversionistas: 45</t>
         </is>
       </c>
     </row>
@@ -9067,19 +8869,19 @@
       <c r="J5" s="11" t="n">
         <v>1074.93</v>
       </c>
-      <c r="K5" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" s="11" t="n">
+      <c r="K5" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="10" t="n">
         <v>1074.93</v>
       </c>
       <c r="M5" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N5" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" s="11" t="n">
+      <c r="N5" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="10" t="n">
         <v>100000</v>
       </c>
     </row>
@@ -9120,19 +8922,19 @@
       <c r="J6" s="17" t="n">
         <v>322.48</v>
       </c>
-      <c r="K6" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="17" t="n">
+      <c r="K6" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="16" t="n">
         <v>322.48</v>
       </c>
       <c r="M6" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="N6" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" s="17" t="n">
+      <c r="N6" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="16" t="n">
         <v>30000</v>
       </c>
     </row>
@@ -9173,19 +8975,19 @@
       <c r="J7" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="K7" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="11" t="n">
+      <c r="K7" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="10" t="n">
         <v>0</v>
       </c>
       <c r="M7" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N7" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" s="11" t="n">
+      <c r="N7" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="10" t="n">
         <v>102900.26</v>
       </c>
     </row>
@@ -9226,19 +9028,19 @@
       <c r="J8" s="17" t="n">
         <v>314.31</v>
       </c>
-      <c r="K8" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" s="17" t="n">
+      <c r="K8" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="16" t="n">
         <v>314.31</v>
       </c>
       <c r="M8" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="N8" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" s="17" t="n">
+      <c r="N8" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="16" t="n">
         <v>25584.8</v>
       </c>
     </row>
@@ -9279,19 +9081,19 @@
       <c r="J9" s="11" t="n">
         <v>913.6900000000001</v>
       </c>
-      <c r="K9" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" s="11" t="n">
+      <c r="K9" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="10" t="n">
         <v>913.6900000000001</v>
       </c>
       <c r="M9" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N9" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" s="11" t="n">
+      <c r="N9" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="10" t="n">
         <v>70000</v>
       </c>
     </row>
@@ -9332,19 +9134,19 @@
       <c r="J10" s="17" t="n">
         <v>233.21</v>
       </c>
-      <c r="K10" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" s="17" t="n">
+      <c r="K10" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="16" t="n">
         <v>233.21</v>
       </c>
       <c r="M10" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="N10" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" s="17" t="n">
+      <c r="N10" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="16" t="n">
         <v>20000</v>
       </c>
     </row>
@@ -9385,19 +9187,19 @@
       <c r="J11" s="11" t="n">
         <v>108.27</v>
       </c>
-      <c r="K11" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" s="11" t="n">
+      <c r="K11" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="10" t="n">
         <v>108.27</v>
       </c>
       <c r="M11" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N11" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" s="11" t="n">
+      <c r="N11" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="10" t="n">
         <v>20000</v>
       </c>
     </row>
@@ -9438,19 +9240,19 @@
       <c r="J12" s="17" t="n">
         <v>368.55</v>
       </c>
-      <c r="K12" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" s="17" t="n">
+      <c r="K12" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="16" t="n">
         <v>368.55</v>
       </c>
       <c r="M12" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="N12" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" s="17" t="n">
+      <c r="N12" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="16" t="n">
         <v>30000</v>
       </c>
     </row>
@@ -9491,19 +9293,19 @@
       <c r="J13" s="11" t="n">
         <v>261.05</v>
       </c>
-      <c r="K13" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" s="11" t="n">
+      <c r="K13" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="10" t="n">
         <v>261.05</v>
       </c>
       <c r="M13" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N13" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" s="11" t="n">
+      <c r="N13" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="10" t="n">
         <v>20000</v>
       </c>
     </row>
@@ -9544,19 +9346,19 @@
       <c r="J14" s="17" t="n">
         <v>515.58</v>
       </c>
-      <c r="K14" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" s="17" t="n">
+      <c r="K14" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="16" t="n">
         <v>515.58</v>
       </c>
       <c r="M14" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="N14" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" s="17" t="n">
+      <c r="N14" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="16" t="n">
         <v>39500</v>
       </c>
     </row>
@@ -9597,19 +9399,19 @@
       <c r="J15" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="K15" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" s="11" t="n">
+      <c r="K15" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="10" t="n">
         <v>0</v>
       </c>
       <c r="M15" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N15" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" s="11" t="n">
+      <c r="N15" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" s="10" t="n">
         <v>81860.05</v>
       </c>
     </row>
@@ -9650,19 +9452,19 @@
       <c r="J16" s="17" t="n">
         <v>675.67</v>
       </c>
-      <c r="K16" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" s="17" t="n">
+      <c r="K16" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="16" t="n">
         <v>675.67</v>
       </c>
       <c r="M16" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="N16" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" s="17" t="n">
+      <c r="N16" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" s="16" t="n">
         <v>55000</v>
       </c>
     </row>
@@ -9703,19 +9505,19 @@
       <c r="J17" s="11" t="n">
         <v>491.4</v>
       </c>
-      <c r="K17" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" s="11" t="n">
+      <c r="K17" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="10" t="n">
         <v>491.4</v>
       </c>
       <c r="M17" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N17" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" s="11" t="n">
+      <c r="N17" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" s="10" t="n">
         <v>40000</v>
       </c>
     </row>
@@ -9756,19 +9558,19 @@
       <c r="J18" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="K18" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" s="17" t="n">
+      <c r="K18" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="16" t="n">
         <v>0</v>
       </c>
       <c r="M18" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="N18" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" s="17" t="n">
+      <c r="N18" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" s="16" t="n">
         <v>25228.37</v>
       </c>
     </row>
@@ -9809,19 +9611,19 @@
       <c r="J19" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="K19" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" s="11" t="n">
+      <c r="K19" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="10" t="n">
         <v>0</v>
       </c>
       <c r="M19" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N19" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" s="11" t="n">
+      <c r="N19" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" s="10" t="n">
         <v>38881.61</v>
       </c>
     </row>
@@ -9862,19 +9664,19 @@
       <c r="J20" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="K20" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" s="17" t="n">
+      <c r="K20" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="16" t="n">
         <v>0</v>
       </c>
       <c r="M20" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="N20" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" s="17" t="n">
+      <c r="N20" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" s="16" t="n">
         <v>40522.11</v>
       </c>
     </row>
@@ -9915,19 +9717,19 @@
       <c r="J21" s="11" t="n">
         <v>403.1</v>
       </c>
-      <c r="K21" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" s="11" t="n">
+      <c r="K21" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="10" t="n">
         <v>403.1</v>
       </c>
       <c r="M21" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N21" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" s="11" t="n">
+      <c r="N21" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" s="10" t="n">
         <v>35000</v>
       </c>
     </row>
@@ -9968,19 +9770,19 @@
       <c r="J22" s="17" t="n">
         <v>245.7</v>
       </c>
-      <c r="K22" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" s="17" t="n">
+      <c r="K22" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="16" t="n">
         <v>245.7</v>
       </c>
       <c r="M22" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="N22" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" s="17" t="n">
+      <c r="N22" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" s="16" t="n">
         <v>20000</v>
       </c>
     </row>
@@ -9995,7 +9797,7 @@
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>Salas Gómez Alfredo</t>
+          <t xml:space="preserve">Salas Gómez Alfredo </t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
@@ -10021,19 +9823,19 @@
       <c r="J23" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="K23" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" s="11" t="n">
+      <c r="K23" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" s="10" t="n">
         <v>0</v>
       </c>
       <c r="M23" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N23" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" s="11" t="n">
+      <c r="N23" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" s="10" t="n">
         <v>31126.1</v>
       </c>
     </row>
@@ -10074,19 +9876,19 @@
       <c r="J24" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="K24" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" s="17" t="n">
+      <c r="K24" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="16" t="n">
         <v>0</v>
       </c>
       <c r="M24" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="N24" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" s="17" t="n">
+      <c r="N24" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" s="16" t="n">
         <v>45317.78</v>
       </c>
     </row>
@@ -10127,19 +9929,19 @@
       <c r="J25" s="11" t="n">
         <v>319.41</v>
       </c>
-      <c r="K25" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" s="11" t="n">
+      <c r="K25" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="10" t="n">
         <v>319.41</v>
       </c>
       <c r="M25" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N25" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" s="11" t="n">
+      <c r="N25" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" s="10" t="n">
         <v>26000</v>
       </c>
     </row>
@@ -10180,19 +9982,19 @@
       <c r="J26" s="17" t="n">
         <v>652.64</v>
       </c>
-      <c r="K26" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" s="17" t="n">
+      <c r="K26" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="16" t="n">
         <v>652.64</v>
       </c>
       <c r="M26" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="N26" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" s="17" t="n">
+      <c r="N26" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" s="16" t="n">
         <v>50000</v>
       </c>
     </row>
@@ -10233,19 +10035,19 @@
       <c r="J27" s="11" t="n">
         <v>245.7</v>
       </c>
-      <c r="K27" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" s="11" t="n">
+      <c r="K27" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="10" t="n">
         <v>245.7</v>
       </c>
       <c r="M27" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N27" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" s="11" t="n">
+      <c r="N27" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" s="10" t="n">
         <v>20000</v>
       </c>
     </row>
@@ -10286,19 +10088,19 @@
       <c r="J28" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="K28" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" s="17" t="n">
+      <c r="K28" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="16" t="n">
         <v>0</v>
       </c>
       <c r="M28" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="N28" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" s="17" t="n">
+      <c r="N28" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" s="16" t="n">
         <v>58463.87</v>
       </c>
     </row>
@@ -10339,19 +10141,19 @@
       <c r="J29" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="K29" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" s="11" t="n">
+      <c r="K29" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="10" t="n">
         <v>0</v>
       </c>
       <c r="M29" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N29" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" s="11" t="n">
+      <c r="N29" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" s="10" t="n">
         <v>67629.08</v>
       </c>
     </row>
@@ -10392,19 +10194,19 @@
       <c r="J30" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="K30" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" s="17" t="n">
+      <c r="K30" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" s="16" t="n">
         <v>0</v>
       </c>
       <c r="M30" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="N30" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" s="17" t="n">
+      <c r="N30" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" s="16" t="n">
         <v>29000.58</v>
       </c>
     </row>
@@ -10445,19 +10247,19 @@
       <c r="J31" s="11" t="n">
         <v>1305.27</v>
       </c>
-      <c r="K31" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" s="11" t="n">
+      <c r="K31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" s="10" t="n">
         <v>1305.27</v>
       </c>
       <c r="M31" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N31" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" s="11" t="n">
+      <c r="N31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" s="10" t="n">
         <v>100000</v>
       </c>
     </row>
@@ -10498,19 +10300,19 @@
       <c r="J32" s="17" t="n">
         <v>230.35</v>
       </c>
-      <c r="K32" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" s="17" t="n">
+      <c r="K32" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="16" t="n">
         <v>230.35</v>
       </c>
       <c r="M32" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="N32" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" s="17" t="n">
+      <c r="N32" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" s="16" t="n">
         <v>20000</v>
       </c>
     </row>
@@ -10551,19 +10353,19 @@
       <c r="J33" s="11" t="n">
         <v>230.35</v>
       </c>
-      <c r="K33" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" s="11" t="n">
+      <c r="K33" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="10" t="n">
         <v>230.35</v>
       </c>
       <c r="M33" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N33" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" s="11" t="n">
+      <c r="N33" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" s="10" t="n">
         <v>20000</v>
       </c>
     </row>
@@ -10604,19 +10406,19 @@
       <c r="J34" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="K34" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" s="17" t="n">
+      <c r="K34" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="16" t="n">
         <v>0</v>
       </c>
       <c r="M34" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="N34" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" s="17" t="n">
+      <c r="N34" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" s="16" t="n">
         <v>22409.39</v>
       </c>
     </row>
@@ -10657,19 +10459,19 @@
       <c r="J35" s="11" t="n">
         <v>1305.27</v>
       </c>
-      <c r="K35" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" s="11" t="n">
+      <c r="K35" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="10" t="n">
         <v>1305.27</v>
       </c>
       <c r="M35" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N35" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" s="11" t="n">
+      <c r="N35" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" s="10" t="n">
         <v>100000</v>
       </c>
     </row>
@@ -10710,19 +10512,19 @@
       <c r="J36" s="17" t="n">
         <v>1305.27</v>
       </c>
-      <c r="K36" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" s="17" t="n">
+      <c r="K36" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="16" t="n">
         <v>1305.27</v>
       </c>
       <c r="M36" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="N36" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" s="17" t="n">
+      <c r="N36" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" s="16" t="n">
         <v>100000</v>
       </c>
     </row>
@@ -10763,19 +10565,19 @@
       <c r="J37" s="11" t="n">
         <v>230.35</v>
       </c>
-      <c r="K37" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" s="11" t="n">
+      <c r="K37" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" s="10" t="n">
         <v>230.35</v>
       </c>
       <c r="M37" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N37" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O37" s="11" t="n">
+      <c r="N37" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" s="10" t="n">
         <v>20000</v>
       </c>
     </row>
@@ -10816,19 +10618,19 @@
       <c r="J38" s="17" t="n">
         <v>614.25</v>
       </c>
-      <c r="K38" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" s="17" t="n">
+      <c r="K38" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" s="16" t="n">
         <v>614.25</v>
       </c>
       <c r="M38" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="N38" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" s="17" t="n">
+      <c r="N38" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" s="16" t="n">
         <v>50000</v>
       </c>
     </row>
@@ -10838,7 +10640,7 @@
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>NSGUSD02-043.20250207.20251231</t>
+          <t>NSGPEN03-017.20160101.20251231</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
@@ -10869,19 +10671,19 @@
       <c r="J39" s="11" t="n">
         <v>345.52</v>
       </c>
-      <c r="K39" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" s="11" t="n">
+      <c r="K39" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" s="10" t="n">
         <v>345.52</v>
       </c>
       <c r="M39" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N39" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" s="11" t="n">
+      <c r="N39" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" s="10" t="n">
         <v>30000</v>
       </c>
     </row>
@@ -10922,19 +10724,19 @@
       <c r="J40" s="17" t="n">
         <v>614.25</v>
       </c>
-      <c r="K40" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L40" s="17" t="n">
+      <c r="K40" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="16" t="n">
         <v>614.25</v>
       </c>
       <c r="M40" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="N40" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O40" s="17" t="n">
+      <c r="N40" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" s="16" t="n">
         <v>50000</v>
       </c>
     </row>
@@ -10975,19 +10777,19 @@
       <c r="J41" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="K41" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" s="11" t="n">
+      <c r="K41" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" s="10" t="n">
         <v>0</v>
       </c>
       <c r="M41" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N41" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O41" s="11" t="n">
+      <c r="N41" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" s="10" t="n">
         <v>64277.78</v>
       </c>
     </row>
@@ -11028,19 +10830,19 @@
       <c r="J42" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="K42" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L42" s="17" t="n">
+      <c r="K42" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" s="16" t="n">
         <v>0</v>
       </c>
       <c r="M42" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="N42" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O42" s="17" t="n">
+      <c r="N42" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" s="16" t="n">
         <v>42851.79</v>
       </c>
     </row>
@@ -11055,7 +10857,7 @@
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>Alcántara Cerna Alfredo</t>
+          <t xml:space="preserve">Alcántara Cerna Alfredo </t>
         </is>
       </c>
       <c r="D43" s="9" t="inlineStr">
@@ -11081,19 +10883,19 @@
       <c r="J43" s="11" t="n">
         <v>575.85</v>
       </c>
-      <c r="K43" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" s="11" t="n">
+      <c r="K43" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" s="10" t="n">
         <v>575.85</v>
       </c>
       <c r="M43" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N43" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O43" s="11" t="n">
+      <c r="N43" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" s="10" t="n">
         <v>50000</v>
       </c>
     </row>
@@ -11134,19 +10936,19 @@
       <c r="J44" s="17" t="n">
         <v>391.58</v>
       </c>
-      <c r="K44" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" s="17" t="n">
+      <c r="K44" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" s="16" t="n">
         <v>391.58</v>
       </c>
       <c r="M44" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="N44" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O44" s="17" t="n">
+      <c r="N44" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" s="16" t="n">
         <v>30000</v>
       </c>
     </row>
@@ -11187,19 +10989,19 @@
       <c r="J45" s="11" t="n">
         <v>376.23</v>
       </c>
-      <c r="K45" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" s="11" t="n">
+      <c r="K45" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" s="10" t="n">
         <v>376.23</v>
       </c>
       <c r="M45" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N45" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O45" s="11" t="n">
+      <c r="N45" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" s="10" t="n">
         <v>35000</v>
       </c>
     </row>
@@ -11240,19 +11042,19 @@
       <c r="J46" s="17" t="n">
         <v>921.37</v>
       </c>
-      <c r="K46" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" s="17" t="n">
+      <c r="K46" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" s="16" t="n">
         <v>921.37</v>
       </c>
       <c r="M46" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="N46" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O46" s="17" t="n">
+      <c r="N46" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" s="16" t="n">
         <v>80000</v>
       </c>
     </row>
@@ -11293,19 +11095,19 @@
       <c r="J47" s="11" t="n">
         <v>737.1</v>
       </c>
-      <c r="K47" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L47" s="11" t="n">
+      <c r="K47" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" s="10" t="n">
         <v>737.1</v>
       </c>
       <c r="M47" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N47" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O47" s="11" t="n">
+      <c r="N47" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" s="10" t="n">
         <v>60000</v>
       </c>
     </row>
@@ -11346,19 +11148,19 @@
       <c r="J48" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="K48" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" s="17" t="n">
+      <c r="K48" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" s="16" t="n">
         <v>0</v>
       </c>
       <c r="M48" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="N48" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O48" s="17" t="n">
+      <c r="N48" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" s="16" t="n">
         <v>51597.82</v>
       </c>
     </row>
@@ -11399,135 +11201,84 @@
       <c r="J49" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="K49" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" s="11" t="n">
+      <c r="K49" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" s="10" t="n">
         <v>0</v>
       </c>
       <c r="M49" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N49" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O49" s="11" t="n">
+      <c r="N49" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" s="10" t="n">
         <v>51828.83</v>
       </c>
     </row>
-    <row r="50" ht="19" customHeight="1">
-      <c r="A50" s="12" t="n">
+    <row r="50" ht="22" customHeight="1">
+      <c r="A50" s="18" t="inlineStr"/>
+      <c r="B50" s="19" t="inlineStr"/>
+      <c r="C50" s="19" t="inlineStr">
+        <is>
+          <t>TOTALES NSGUSD02 (USD)</t>
+        </is>
+      </c>
+      <c r="D50" s="18" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E50" s="20">
+        <f>SUM(E5:E49)</f>
         <v/>
       </c>
-      <c r="B50" s="13" t="n">
+      <c r="F50" s="20">
+        <f>SUM(F5:F49)</f>
         <v/>
       </c>
-      <c r="C50" s="14" t="inlineStr">
-        <is>
-          <t>TOTALES NSGUSD02 (USD)</t>
-        </is>
-      </c>
-      <c r="D50" s="15" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="E50" s="16" t="n">
+      <c r="G50" s="20">
+        <f>SUM(G5:G49)</f>
         <v/>
       </c>
-      <c r="F50" s="16" t="n">
+      <c r="H50" s="20">
+        <f>SUM(H5:H49)</f>
         <v/>
       </c>
-      <c r="G50" s="17" t="n">
+      <c r="I50" s="20">
+        <f>SUM(I5:I49)</f>
         <v/>
       </c>
-      <c r="H50" s="17" t="n">
+      <c r="J50" s="20">
+        <f>SUM(J5:J49)</f>
         <v/>
       </c>
-      <c r="I50" s="17" t="n">
+      <c r="K50" s="20">
+        <f>SUM(K5:K49)</f>
         <v/>
       </c>
-      <c r="J50" s="17" t="n">
+      <c r="L50" s="20">
+        <f>SUM(L5:L49)</f>
         <v/>
       </c>
-      <c r="K50" s="16" t="n">
+      <c r="M50" s="20">
+        <f>SUM(M5:M49)</f>
         <v/>
       </c>
-      <c r="L50" s="17" t="n">
+      <c r="N50" s="20">
+        <f>SUM(N5:N49)</f>
         <v/>
       </c>
-      <c r="M50" s="17" t="n">
-        <v/>
-      </c>
-      <c r="N50" s="16" t="n">
-        <v/>
-      </c>
-      <c r="O50" s="17" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="51" ht="22" customHeight="1">
-      <c r="A51" s="18" t="inlineStr"/>
-      <c r="B51" s="19" t="inlineStr"/>
-      <c r="C51" s="19" t="inlineStr">
-        <is>
-          <t>TOTALES NSGUSD02 (USD)</t>
-        </is>
-      </c>
-      <c r="D51" s="18" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="E51" s="20">
-        <f>SUM(E5:E50)</f>
-        <v/>
-      </c>
-      <c r="F51" s="20">
-        <f>SUM(F5:F50)</f>
-        <v/>
-      </c>
-      <c r="G51" s="20">
-        <f>SUM(G5:G50)</f>
-        <v/>
-      </c>
-      <c r="H51" s="20">
-        <f>SUM(H5:H50)</f>
-        <v/>
-      </c>
-      <c r="I51" s="20">
-        <f>SUM(I5:I50)</f>
-        <v/>
-      </c>
-      <c r="J51" s="20">
-        <f>SUM(J5:J50)</f>
-        <v/>
-      </c>
-      <c r="K51" s="20">
-        <f>SUM(K5:K50)</f>
-        <v/>
-      </c>
-      <c r="L51" s="20">
-        <f>SUM(L5:L50)</f>
-        <v/>
-      </c>
-      <c r="M51" s="20">
-        <f>SUM(M5:M50)</f>
-        <v/>
-      </c>
-      <c r="N51" s="20">
-        <f>SUM(N5:N50)</f>
-        <v/>
-      </c>
-      <c r="O51" s="20">
-        <f>SUM(O5:O50)</f>
+      <c r="O50" s="20">
+        <f>SUM(O5:O49)</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:N2"/>
-    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A2:O2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
